--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E527636B-0A8B-40F1-81C6-614DDE3390C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{E527636B-0A8B-40F1-81C6-614DDE3390C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35DB7806-0A95-4B70-B6D6-C8926364C563}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
@@ -22,9 +22,11 @@
     <sheet name="08-09" sheetId="7" r:id="rId7"/>
     <sheet name="09-09" sheetId="8" r:id="rId8"/>
     <sheet name="10-09" sheetId="9" r:id="rId9"/>
+    <sheet name="13-09" sheetId="10" r:id="rId10"/>
+    <sheet name="14-09" sheetId="11" r:id="rId11"/>
+    <sheet name="15-09" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="184">
   <si>
     <t>Date</t>
   </si>
@@ -475,6 +477,132 @@
   </si>
   <si>
     <t>Date ACC</t>
+  </si>
+  <si>
+    <t>0683ICS0020</t>
+  </si>
+  <si>
+    <t>HMMU433444 /9</t>
+  </si>
+  <si>
+    <t>26H0108168</t>
+  </si>
+  <si>
+    <t>SEGU585325 /8</t>
+  </si>
+  <si>
+    <t>26H0108169</t>
+  </si>
+  <si>
+    <t>OPT</t>
+  </si>
+  <si>
+    <t>MEDU760577 /9</t>
+  </si>
+  <si>
+    <t>MA526075</t>
+  </si>
+  <si>
+    <t>MSDU787252 /0</t>
+  </si>
+  <si>
+    <t>MA526074</t>
+  </si>
+  <si>
+    <t>00017-511-31</t>
+  </si>
+  <si>
+    <t>BMOU213576 /9</t>
+  </si>
+  <si>
+    <t>2134430</t>
+  </si>
+  <si>
+    <t>CXSU114000 /6</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>FLAT</t>
+  </si>
+  <si>
+    <t>TCLU600602 /5</t>
+  </si>
+  <si>
+    <t>00183-524-31</t>
+  </si>
+  <si>
+    <t>00426-510-31</t>
+  </si>
+  <si>
+    <t>APZU213305 /9</t>
+  </si>
+  <si>
+    <t>CMAU194208 /0</t>
+  </si>
+  <si>
+    <t>TEMU387154 /1</t>
+  </si>
+  <si>
+    <t>MRKU714747 /1</t>
+  </si>
+  <si>
+    <t>MRKU776760 /0</t>
+  </si>
+  <si>
+    <t>MRKU862304 /2</t>
+  </si>
+  <si>
+    <t>MSKU561006 /4</t>
+  </si>
+  <si>
+    <t>SUDU747145 /0</t>
+  </si>
+  <si>
+    <t>TCKU302077 /9</t>
+  </si>
+  <si>
+    <t>TEMU342001 /8</t>
+  </si>
+  <si>
+    <t>TCNU628382 /9</t>
+  </si>
+  <si>
+    <t>M9768365</t>
+  </si>
+  <si>
+    <t>MSNU975917 /4</t>
+  </si>
+  <si>
+    <t>5055347</t>
+  </si>
+  <si>
+    <t>MSDU612394 /9</t>
+  </si>
+  <si>
+    <t>2139541</t>
+  </si>
+  <si>
+    <t>XXXU459750 /8</t>
+  </si>
+  <si>
+    <t>LB0268891</t>
+  </si>
+  <si>
+    <t>0246ICS0005</t>
+  </si>
+  <si>
+    <t>0165ICS0071</t>
+  </si>
+  <si>
+    <t>0165ICS0016</t>
+  </si>
+  <si>
+    <t>0038ICS0013</t>
+  </si>
+  <si>
+    <t>HUISSIER +RECETTE+DOUANE</t>
   </si>
 </sst>
 </file>
@@ -485,7 +613,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,8 +740,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,8 +806,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -805,11 +949,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -990,7 +1156,13 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1001,6 +1173,37 @@
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1063,6 +1266,116 @@
         <a:xfrm>
           <a:off x="180975" y="0"/>
           <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5D4AF65-81E3-466F-8159-3A9F12D30476}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="457197"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A247E0F-C4DB-4AFF-8AD8-F0B049EC9FD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="476247"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1459,6 +1772,65 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9EF49A0-47E2-49A9-B570-BD1329178EE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="438147"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -1967,15 +2339,15 @@
       </c>
       <c r="B9" s="3">
         <f>'10-09'!H1</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
         <f>'10-09'!H2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -2105,15 +2477,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2121,6 +2493,1801 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C8F5FD-19B1-4E48-8880-94629C3B00D2}">
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="68"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="68"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="68"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3575</v>
+      </c>
+      <c r="F22" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="58">
+        <v>3576</v>
+      </c>
+      <c r="F23" s="25">
+        <v>40</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="25"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="25"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C37" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" s="29">
+        <v>3554</v>
+      </c>
+      <c r="F37" s="71">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="29">
+        <v>0</v>
+      </c>
+      <c r="F38" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C39" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="29">
+        <v>0</v>
+      </c>
+      <c r="F39" s="71" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="39"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="39"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="40">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="40">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F17 F37:F39" xr:uid="{477DA8D9-A8D5-4C4E-8278-E67C3D88C529}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43 F18" xr:uid="{5853D75A-A2FC-46E5-9849-55E8D1E71EC6}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B74228C-535B-4DB4-808D-EEA54E82FBF2}">
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="73">
+        <v>14092026</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="18">
+        <v>313157</v>
+      </c>
+      <c r="F8" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="68"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="68"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="68"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3552</v>
+      </c>
+      <c r="F22" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19">
+        <v>13092026</v>
+      </c>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" s="58">
+        <v>3551</v>
+      </c>
+      <c r="F23" s="25">
+        <v>40</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="25"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="25"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="71"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="71"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="71"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="39"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="39"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="40">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="40">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43 F18" xr:uid="{0AFD59BA-583F-4C95-AC51-CAAF9556C872}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17" xr:uid="{F399C93B-FD8F-4D0D-8BEC-B79CC3D65A0A}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F154D21-9CAD-4065-B54D-D0B6ECCC7A19}">
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="75">
+        <v>15092026</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="75">
+        <v>15092026</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="75">
+        <v>15092026</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="75">
+        <v>15092026</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="68"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="25"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="25"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="25"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="74"/>
+      <c r="E37" s="29">
+        <v>3602</v>
+      </c>
+      <c r="F37" s="71">
+        <v>20</v>
+      </c>
+      <c r="G37" s="78" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="74"/>
+      <c r="E38" s="29">
+        <v>3603</v>
+      </c>
+      <c r="F38" s="71">
+        <v>20</v>
+      </c>
+      <c r="G38" s="78"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="74"/>
+      <c r="E39" s="29">
+        <v>3601</v>
+      </c>
+      <c r="F39" s="71">
+        <v>20</v>
+      </c>
+      <c r="G39" s="78"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="74"/>
+      <c r="E40" s="29">
+        <v>3609</v>
+      </c>
+      <c r="F40" s="39">
+        <v>20</v>
+      </c>
+      <c r="G40" s="78"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="29">
+        <v>3606</v>
+      </c>
+      <c r="E41" s="29">
+        <v>3553</v>
+      </c>
+      <c r="F41" s="29">
+        <v>20</v>
+      </c>
+      <c r="G41" s="78"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="74"/>
+      <c r="E42" s="29">
+        <v>3607</v>
+      </c>
+      <c r="F42" s="29">
+        <v>20</v>
+      </c>
+      <c r="G42" s="78"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="74"/>
+      <c r="E43" s="29">
+        <v>3605</v>
+      </c>
+      <c r="F43" s="29">
+        <v>20</v>
+      </c>
+      <c r="G43" s="78"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="74"/>
+      <c r="E44" s="29">
+        <v>3610</v>
+      </c>
+      <c r="F44" s="29">
+        <v>20</v>
+      </c>
+      <c r="G44" s="78"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>9</v>
+      </c>
+      <c r="B45" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="74"/>
+      <c r="E45" s="29">
+        <v>3608</v>
+      </c>
+      <c r="F45" s="29">
+        <v>20</v>
+      </c>
+      <c r="G45" s="78"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>10</v>
+      </c>
+      <c r="B46" s="19">
+        <v>15092026</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="74"/>
+      <c r="E46" s="29">
+        <v>3604</v>
+      </c>
+      <c r="F46" s="29">
+        <v>20</v>
+      </c>
+      <c r="G46" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G37:G46"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17" xr:uid="{BE976A68-E648-4F40-966B-6A401B30B1D2}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18" xr:uid="{A6C20A5E-C2BD-41E8-A206-5A78C74926B4}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2173,16 +4340,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2787,16 +4954,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3350,16 +5517,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3903,16 +6070,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4423,16 +6590,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5008,16 +7175,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5474,7 +7641,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F55FDF-6DCB-4DDA-B827-6D1FD6BE3879}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -5492,7 +7659,7 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C31,"&lt;&gt;")</f>
+        <f>COUNTIF(C8:C24,"&lt;&gt;")</f>
         <v>11</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -5502,35 +7669,35 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B36:B45,"&lt;&gt;",C36:C45,"VH")</f>
+        <f>COUNTIFS(B29:B30,"&lt;&gt;",C29:C30,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C36:C45)-F2</f>
+        <f>COUNTA(C29:C30)-F2</f>
         <v>0</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E36:E45,"VIDE")</f>
+        <f>COUNTIF(E29:E30,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5685,7 +7852,7 @@
       <c r="B13" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="18" t="s">
         <v>112</v>
       </c>
@@ -5722,10 +7889,10 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="69"/>
       <c r="D15" s="24" t="s">
         <v>117</v>
       </c>
@@ -5741,8 +7908,8 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="19"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
       </c>
@@ -5754,12 +7921,12 @@
       </c>
       <c r="G16" s="61"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="19"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
       </c>
@@ -5771,12 +7938,12 @@
       </c>
       <c r="G17" s="61"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="19"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
       </c>
@@ -5788,11 +7955,11 @@
       </c>
       <c r="G18" s="61"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="64"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -5807,11 +7974,11 @@
       </c>
       <c r="G19" s="61"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="65"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -5826,7 +7993,7 @@
       </c>
       <c r="G20" s="61"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>14</v>
       </c>
@@ -5847,7 +8014,7 @@
       </c>
       <c r="G21" s="61"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>15</v>
       </c>
@@ -5868,7 +8035,7 @@
       </c>
       <c r="G22" s="61"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>16</v>
       </c>
@@ -5889,14 +8056,14 @@
       </c>
       <c r="G23" s="61"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>17</v>
       </c>
       <c r="B24" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="69"/>
       <c r="D24" s="24" t="s">
         <v>139</v>
       </c>
@@ -5908,394 +8075,200 @@
       </c>
       <c r="G24" s="61"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
-        <v>18</v>
-      </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="61"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
-        <v>19</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="61"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="61"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+    </row>
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="61"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
+      <c r="C28" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="61"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="17">
+      <c r="D28" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>1</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>2</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="25"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="61"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="17">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="61"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="16" t="s">
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>9092026</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" s="39">
+        <v>3577</v>
+      </c>
+      <c r="F35" s="39">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
-        <v>1</v>
-      </c>
-      <c r="B36" s="19">
-        <v>7092026</v>
-      </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="29"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="25"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="25"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="29"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="18"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="25"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="25">
-        <v>5</v>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="25"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="25">
-        <v>6</v>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="23"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
       <c r="F41" s="25"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25">
-        <v>7</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="25"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="25">
-        <v>8</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="25"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="25">
-        <v>9</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="25"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>10</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="25"/>
-    </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
-        <v>11</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="25"/>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="35"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="35"/>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-      <c r="B48" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="25">
-        <v>1</v>
-      </c>
-      <c r="B51" s="19">
-        <v>9092026</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E51" s="39">
-        <v>3577</v>
-      </c>
-      <c r="F51" s="39">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25">
-        <v>2</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="25">
-        <v>3</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="25">
-        <v>4</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="25">
-        <v>5</v>
-      </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="40">
-        <v>6</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="40">
-        <v>7</v>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="25"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F58" s="41"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6303,22 +8276,23 @@
     <mergeCell ref="B15:B20"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F57 F32" xr:uid="{C60EBE37-60DD-4590-A805-1B082306F56F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F25" xr:uid="{C60EBE37-60DD-4590-A805-1B082306F56F}">
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F31" xr:uid="{38E0B31F-E63B-4BBF-A034-5D91A0C57AEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F24" xr:uid="{38E0B31F-E63B-4BBF-A034-5D91A0C57AEC}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E81CCA-C2A4-4E26-88A6-3C25B115BC82}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -6336,8 +8310,8 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C31,"&lt;&gt;")</f>
-        <v>0</v>
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>6</v>
@@ -6346,35 +8320,35 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B36:B45,"&lt;&gt;",C36:C45,"VH")</f>
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C36:C45)-F2</f>
-        <v>0</v>
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E36:E45,"VIDE")</f>
+        <f>COUNTIF(E22:E31,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6385,14 +8359,14 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -6415,38 +8389,44 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="61"/>
+      <c r="B8" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="19">
+        <v>10092026</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" s="18">
+        <v>20</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="19"/>
+      <c r="B9" s="64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D9" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>101</v>
+        <v>143</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>144</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>16</v>
@@ -6457,681 +8437,483 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="19"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D10" s="18" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="61"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="19"/>
+      <c r="B11" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D11" s="18" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="61"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="F11" s="18">
+        <v>20</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="19"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D12" s="18" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="61"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="19"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D13" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" s="18">
-        <v>313157</v>
-      </c>
-      <c r="F13" s="18">
-        <v>40</v>
-      </c>
-      <c r="G13" s="61"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="19"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="19">
+        <v>10092026</v>
+      </c>
       <c r="D14" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>115</v>
+        <v>123</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>124</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="61"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="17">
+      <c r="G14" s="62" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="62"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="62"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="63" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="61"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="17">
+      <c r="B17" s="42"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="61"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>10092026</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3577</v>
+      </c>
+      <c r="F22" s="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="25"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="25"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
         <v>9</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="61"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
         <v>10</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="61"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
         <v>11</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="61"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
-        <v>12</v>
-      </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="61"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
-        <v>13</v>
-      </c>
-      <c r="B20" s="65"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="18">
-        <v>40</v>
-      </c>
-      <c r="G20" s="61"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
-        <v>14</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="18">
-        <v>40</v>
-      </c>
-      <c r="G21" s="61"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
-        <v>15</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="18">
-        <v>40</v>
-      </c>
-      <c r="G22" s="61"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
-        <v>16</v>
-      </c>
-      <c r="B23" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="61"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
-        <v>17</v>
-      </c>
-      <c r="B24" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="18">
-        <v>20</v>
-      </c>
-      <c r="G24" s="61"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
-        <v>18</v>
-      </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="61"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
-        <v>19</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="61"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
-        <v>20</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="61"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
-        <v>21</v>
-      </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="61"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="17">
-        <v>22</v>
-      </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="61"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="17">
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="61"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="17">
-        <v>24</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="61"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="16" t="s">
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="25">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
         <v>1</v>
       </c>
-      <c r="B36" s="19">
-        <v>7092026</v>
-      </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25">
+      <c r="B37" s="19">
+        <v>10092026</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="39">
+        <v>3552</v>
+      </c>
+      <c r="F37" s="39">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
         <v>2</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="25"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="25">
+      <c r="B38" s="19">
+        <v>10092026</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="39">
+        <v>3551</v>
+      </c>
+      <c r="F38" s="39">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
         <v>3</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="25"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="25">
-        <v>4</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="29"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="25"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="29"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="29"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="25"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="29"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="40">
         <v>6</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="25"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25">
+      <c r="B42" s="19"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="40">
         <v>7</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="25"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="25">
-        <v>8</v>
-      </c>
       <c r="B43" s="19"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="30"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="29"/>
       <c r="F43" s="25"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="25">
-        <v>9</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="25"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>10</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="25"/>
-    </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
-        <v>11</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="25"/>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="35"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="35"/>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-      <c r="B48" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="25">
-        <v>1</v>
-      </c>
-      <c r="B51" s="19">
-        <v>9092026</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E51" s="39">
-        <v>3577</v>
-      </c>
-      <c r="F51" s="39">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25">
-        <v>2</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="25">
-        <v>3</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="25">
-        <v>4</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="25">
-        <v>5</v>
-      </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="40">
-        <v>6</v>
-      </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="40">
-        <v>7</v>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="25"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F58" s="41"/>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B14"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F26 F28:F31" xr:uid="{6AE38A2C-D536-43A6-874D-A17F73BC6B4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43 F18" xr:uid="{2C76199B-A1FF-4695-A4B3-E9AFCFD4BC11}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F17" xr:uid="{6AE38A2C-D536-43A6-874D-A17F73BC6B4C}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F57 F32" xr:uid="{2C76199B-A1FF-4695-A4B3-E9AFCFD4BC11}">
-      <formula1>"20,40,45,50"</formula1>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{E527636B-0A8B-40F1-81C6-614DDE3390C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35DB7806-0A95-4B70-B6D6-C8926364C563}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F18BBD0B-AB74-4608-8E25-5334F1B9C144}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,11 @@
     <sheet name="13-09" sheetId="10" r:id="rId10"/>
     <sheet name="14-09" sheetId="11" r:id="rId11"/>
     <sheet name="15-09" sheetId="12" r:id="rId12"/>
+    <sheet name="16-09" sheetId="13" r:id="rId13"/>
+    <sheet name="17-06" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="218">
   <si>
     <t>Date</t>
   </si>
@@ -603,6 +606,108 @@
   </si>
   <si>
     <t>HUISSIER +RECETTE+DOUANE</t>
+  </si>
+  <si>
+    <t>CAIU818783 /6</t>
+  </si>
+  <si>
+    <t>CAIU819501 /9</t>
+  </si>
+  <si>
+    <t>CAXU959721 /0</t>
+  </si>
+  <si>
+    <t>CRSU928503 /0</t>
+  </si>
+  <si>
+    <t>CXDU134311 /3</t>
+  </si>
+  <si>
+    <t>CXDU168050 /0</t>
+  </si>
+  <si>
+    <t>FCGU198565 /0</t>
+  </si>
+  <si>
+    <t>GESU661177 /9</t>
+  </si>
+  <si>
+    <t>HJMU133346 /2</t>
+  </si>
+  <si>
+    <t>HJMU152689 /9</t>
+  </si>
+  <si>
+    <t>SEGU466432 /6</t>
+  </si>
+  <si>
+    <t>TCNU646691 /7</t>
+  </si>
+  <si>
+    <t>TGHU694661 /0</t>
+  </si>
+  <si>
+    <t>TOLU878955 /6</t>
+  </si>
+  <si>
+    <t>GESU575475 /4</t>
+  </si>
+  <si>
+    <t>TEXU895077 /6</t>
+  </si>
+  <si>
+    <t>00539-508-31</t>
+  </si>
+  <si>
+    <t>00704-525-16</t>
+  </si>
+  <si>
+    <t>000355-524-16</t>
+  </si>
+  <si>
+    <t>500058-519-16</t>
+  </si>
+  <si>
+    <t>500132-519-16</t>
+  </si>
+  <si>
+    <t>500114-519-16</t>
+  </si>
+  <si>
+    <t>000710-525-16</t>
+  </si>
+  <si>
+    <t>000679-525-16</t>
+  </si>
+  <si>
+    <t>00692-509-31</t>
+  </si>
+  <si>
+    <t>00358-510-31</t>
+  </si>
+  <si>
+    <t>00112-510-31</t>
+  </si>
+  <si>
+    <t>ECMU266869 /7</t>
+  </si>
+  <si>
+    <t>00164-513-31</t>
+  </si>
+  <si>
+    <t>000704-525-16</t>
+  </si>
+  <si>
+    <t>000354-524-16</t>
+  </si>
+  <si>
+    <t>000677-525-16</t>
+  </si>
+  <si>
+    <t>500114 et 00355-524</t>
+  </si>
+  <si>
+    <t>500054 et 00679-525</t>
   </si>
 </sst>
 </file>
@@ -613,7 +718,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -750,6 +855,11 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -813,7 +923,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -971,11 +1081,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1159,21 +1285,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1189,10 +1300,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,12 +1309,43 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{916521BF-F3AB-4A1E-83AD-7A0FE5592B6D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1376,6 +1514,116 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="476247"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4A7479D-1B26-4037-BF41-BAD2AE3EDAF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C0DDB3A-BA0A-41B7-92C4-226B3AF87C83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="495297"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1827,10 +2075,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2328,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:D9" si="1">SUM(B8:C8)</f>
+        <f t="shared" ref="D8:D14" si="1">SUM(B8:C8)</f>
         <v>11</v>
       </c>
       <c r="F8" s="3"/>
@@ -2355,54 +2599,108 @@
       <c r="A10" s="2">
         <v>46274</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="B10" s="3">
+        <f>'10-09'!H2</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'10-09'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46275</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
+      <c r="B11" s="3">
+        <f>'10-09'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <f>'10-09'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
+        <v>46278</v>
+      </c>
+      <c r="B12" s="3">
+        <f>'13-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <f>'13-09'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
+        <v>46279</v>
+      </c>
+      <c r="B13" s="3">
+        <f>'14-09'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <f>'14-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46278</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
+        <v>46280</v>
+      </c>
+      <c r="B14" s="3">
+        <f>'15-09'!H1</f>
+        <v>4</v>
+      </c>
+      <c r="C14" s="3">
+        <f>'10-09'!H2</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46279</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
+        <v>46281</v>
+      </c>
+      <c r="B15" s="3">
+        <f>'16-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <f>'16-09'!H2</f>
+        <v>12</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" ref="D15" si="2">SUM(B15:C15)</f>
+        <v>12</v>
+      </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -2477,15 +2775,15 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B22)</f>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2545,16 +2843,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -2606,7 +2904,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="68"/>
+      <c r="B9" s="63"/>
       <c r="C9" s="19"/>
       <c r="D9" s="18"/>
       <c r="E9" s="23"/>
@@ -2616,7 +2914,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="63"/>
       <c r="C10" s="19"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -2626,7 +2924,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="68"/>
+      <c r="B11" s="63"/>
       <c r="C11" s="19"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -2636,7 +2934,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="63"/>
       <c r="C12" s="19"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -2646,7 +2944,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="19"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -2656,7 +2954,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="68"/>
+      <c r="B14" s="63"/>
       <c r="C14" s="19"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
@@ -2950,16 +3248,16 @@
       <c r="B37" s="19">
         <v>13092026</v>
       </c>
-      <c r="C37" s="70" t="s">
+      <c r="C37" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="70" t="s">
+      <c r="D37" s="65" t="s">
         <v>154</v>
       </c>
       <c r="E37" s="29">
         <v>3554</v>
       </c>
-      <c r="F37" s="71">
+      <c r="F37" s="66">
         <v>20</v>
       </c>
     </row>
@@ -2970,16 +3268,16 @@
       <c r="B38" s="19">
         <v>13092026</v>
       </c>
-      <c r="C38" s="72" t="s">
+      <c r="C38" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="71" t="s">
+      <c r="D38" s="66" t="s">
         <v>156</v>
       </c>
       <c r="E38" s="29">
         <v>0</v>
       </c>
-      <c r="F38" s="71" t="s">
+      <c r="F38" s="66" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2990,16 +3288,16 @@
       <c r="B39" s="19">
         <v>13092026</v>
       </c>
-      <c r="C39" s="71" t="s">
+      <c r="C39" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="D39" s="66" t="s">
         <v>156</v>
       </c>
       <c r="E39" s="29">
         <v>0</v>
       </c>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="66" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3114,16 +3412,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3168,7 +3466,7 @@
       <c r="B8" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="19">
         <v>14092026</v>
       </c>
       <c r="D8" s="18" t="s">
@@ -3185,7 +3483,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="68"/>
+      <c r="B9" s="63"/>
       <c r="C9" s="19"/>
       <c r="D9" s="18"/>
       <c r="E9" s="23"/>
@@ -3195,7 +3493,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="68"/>
+      <c r="B10" s="63"/>
       <c r="C10" s="19"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -3205,7 +3503,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="68"/>
+      <c r="B11" s="63"/>
       <c r="C11" s="19"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -3215,7 +3513,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="63"/>
       <c r="C12" s="19"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -3225,7 +3523,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="19"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
@@ -3235,7 +3533,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="68"/>
+      <c r="B14" s="63"/>
       <c r="C14" s="19"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
@@ -3523,30 +3821,30 @@
         <v>1</v>
       </c>
       <c r="B37" s="19"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
       <c r="E37" s="29"/>
-      <c r="F37" s="71"/>
+      <c r="F37" s="66"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
         <v>2</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="71"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="66"/>
       <c r="E38" s="29"/>
-      <c r="F38" s="71"/>
+      <c r="F38" s="66"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
         <v>3</v>
       </c>
       <c r="B39" s="19"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
       <c r="E39" s="29"/>
-      <c r="F39" s="71"/>
+      <c r="F39" s="66"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -3659,16 +3957,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3696,13 +3994,13 @@
       <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="69" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3713,7 +4011,7 @@
       <c r="B8" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="68">
         <v>15092026</v>
       </c>
       <c r="D8" s="24" t="s">
@@ -3730,10 +4028,10 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="68">
         <v>15092026</v>
       </c>
       <c r="D9" s="18" t="s">
@@ -3750,10 +4048,10 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="70" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="68">
         <v>15092026</v>
       </c>
       <c r="D10" s="18" t="s">
@@ -3770,10 +4068,10 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="70" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="68">
         <v>15092026</v>
       </c>
       <c r="D11" s="18" t="s">
@@ -3790,8 +4088,8 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="75"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -3800,8 +4098,8 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="75"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
@@ -3810,8 +4108,8 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="75"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
@@ -3819,7 +4117,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="53"/>
-      <c r="C15" s="75"/>
+      <c r="C15" s="68"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
       <c r="F15" s="18"/>
@@ -3827,7 +4125,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="53"/>
-      <c r="C16" s="75"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
       <c r="F16" s="18"/>
@@ -3837,7 +4135,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="42"/>
-      <c r="C17" s="75"/>
+      <c r="C17" s="68"/>
       <c r="D17" s="24"/>
       <c r="E17" s="23"/>
       <c r="F17" s="18"/>
@@ -4087,14 +4385,14 @@
       <c r="C37" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="74"/>
+      <c r="D37" s="46"/>
       <c r="E37" s="29">
         <v>3602</v>
       </c>
-      <c r="F37" s="71">
+      <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="78" t="s">
+      <c r="G37" s="76" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4108,14 +4406,14 @@
       <c r="C38" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="74"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="29">
         <v>3603</v>
       </c>
-      <c r="F38" s="71">
+      <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="78"/>
+      <c r="G38" s="76"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -4127,14 +4425,14 @@
       <c r="C39" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="D39" s="74"/>
+      <c r="D39" s="46"/>
       <c r="E39" s="29">
         <v>3601</v>
       </c>
-      <c r="F39" s="71">
+      <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="78"/>
+      <c r="G39" s="76"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -4146,14 +4444,14 @@
       <c r="C40" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="74"/>
+      <c r="D40" s="46"/>
       <c r="E40" s="29">
         <v>3609</v>
       </c>
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="78"/>
+      <c r="G40" s="76"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -4174,7 +4472,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="78"/>
+      <c r="G41" s="76"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -4186,14 +4484,14 @@
       <c r="C42" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="74"/>
+      <c r="D42" s="46"/>
       <c r="E42" s="29">
         <v>3607</v>
       </c>
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="78"/>
+      <c r="G42" s="76"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -4205,14 +4503,14 @@
       <c r="C43" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="D43" s="74"/>
+      <c r="D43" s="46"/>
       <c r="E43" s="29">
         <v>3605</v>
       </c>
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="78"/>
+      <c r="G43" s="76"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -4224,14 +4522,14 @@
       <c r="C44" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="74"/>
+      <c r="D44" s="46"/>
       <c r="E44" s="29">
         <v>3610</v>
       </c>
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="78"/>
+      <c r="G44" s="76"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -4243,14 +4541,14 @@
       <c r="C45" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="D45" s="74"/>
+      <c r="D45" s="46"/>
       <c r="E45" s="29">
         <v>3608</v>
       </c>
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="78"/>
+      <c r="G45" s="76"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -4262,14 +4560,14 @@
       <c r="C46" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="D46" s="74"/>
+      <c r="D46" s="46"/>
       <c r="E46" s="29">
         <v>3604</v>
       </c>
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="78"/>
+      <c r="G46" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4288,6 +4586,1504 @@
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477EFD95-392C-46D2-BEA6-1E5A8A7942D2}">
+  <dimension ref="A1:N54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B36,"&lt;&gt;",C22:C36,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C41)-F2</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E36,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D22" s="77" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="39">
+        <v>3561</v>
+      </c>
+      <c r="F22" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="39">
+        <v>3562</v>
+      </c>
+      <c r="F23" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C24" s="27"/>
+      <c r="D24" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="39">
+        <v>3564</v>
+      </c>
+      <c r="F24" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C25" s="27"/>
+      <c r="D25" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="39">
+        <v>3563</v>
+      </c>
+      <c r="F25" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="39">
+        <v>3565</v>
+      </c>
+      <c r="F26" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="39">
+        <v>3566</v>
+      </c>
+      <c r="F27" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="39">
+        <v>3567</v>
+      </c>
+      <c r="F28" s="32">
+        <v>40</v>
+      </c>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="39">
+        <v>3568</v>
+      </c>
+      <c r="F29" s="78">
+        <v>40</v>
+      </c>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="39">
+        <v>3569</v>
+      </c>
+      <c r="F30" s="32">
+        <v>40</v>
+      </c>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="39">
+        <v>3570</v>
+      </c>
+      <c r="F31" s="32">
+        <v>40</v>
+      </c>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C32" s="27"/>
+      <c r="D32" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="39">
+        <v>3503</v>
+      </c>
+      <c r="F32" s="32">
+        <v>40</v>
+      </c>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="25">
+        <v>12</v>
+      </c>
+      <c r="B33" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C33" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="39">
+        <v>3502</v>
+      </c>
+      <c r="F33" s="32">
+        <v>40</v>
+      </c>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
+        <v>13</v>
+      </c>
+      <c r="B34" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C34" s="27"/>
+      <c r="D34" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="39">
+        <v>3501</v>
+      </c>
+      <c r="F34" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>14</v>
+      </c>
+      <c r="B35" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C35" s="27"/>
+      <c r="D35" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>15</v>
+      </c>
+      <c r="B36" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="39">
+        <v>3580</v>
+      </c>
+      <c r="F36" s="32">
+        <v>40</v>
+      </c>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>16</v>
+      </c>
+      <c r="B37" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C37" s="33"/>
+      <c r="D37" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37" s="24"/>
+      <c r="F37" s="32">
+        <v>40</v>
+      </c>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>17</v>
+      </c>
+      <c r="B38" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="29">
+        <v>3554</v>
+      </c>
+      <c r="F38" s="66">
+        <v>20</v>
+      </c>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>18</v>
+      </c>
+      <c r="B39" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="E39" s="29">
+        <v>0</v>
+      </c>
+      <c r="F39" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>19</v>
+      </c>
+      <c r="B40" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="D40" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="29">
+        <v>0</v>
+      </c>
+      <c r="F40" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>20</v>
+      </c>
+      <c r="B41" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" s="25">
+        <v>3943</v>
+      </c>
+      <c r="F41" s="80">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>1</v>
+      </c>
+      <c r="B45" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="29">
+        <v>3556</v>
+      </c>
+      <c r="F45" s="66">
+        <v>40</v>
+      </c>
+      <c r="G45" s="76"/>
+    </row>
+    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>2</v>
+      </c>
+      <c r="B46" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="29">
+        <v>3555</v>
+      </c>
+      <c r="F46" s="18">
+        <v>40</v>
+      </c>
+      <c r="G46" s="76"/>
+    </row>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
+        <v>3</v>
+      </c>
+      <c r="B47" s="19">
+        <v>16092026</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="34">
+        <v>18233786</v>
+      </c>
+      <c r="E47" s="29">
+        <v>3558</v>
+      </c>
+      <c r="F47" s="66">
+        <v>40</v>
+      </c>
+      <c r="G47" s="76"/>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="25">
+        <v>4</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="76"/>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="25">
+        <v>5</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="76"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="25">
+        <v>6</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="76"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="25">
+        <v>7</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="76"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="25">
+        <v>8</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="76"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="25">
+        <v>9</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="76"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="25">
+        <v>10</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="76"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="G45:G54"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22:F37" xr:uid="{891C7987-B10E-436C-8334-E349696CE1DC}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F45:F47 F8:F17 F38:F40" xr:uid="{43175F8C-86E7-45FE-A167-E0EFC0821C3A}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7350925C-618C-42E4-A88C-4B4C613A9259}">
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>8</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="39">
+        <v>3564</v>
+      </c>
+      <c r="F22" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="39">
+        <v>3563</v>
+      </c>
+      <c r="F23" s="32">
+        <v>40</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="39">
+        <v>3566</v>
+      </c>
+      <c r="F24" s="32">
+        <v>40</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="39">
+        <v>3569</v>
+      </c>
+      <c r="F25" s="32">
+        <v>40</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="39">
+        <v>3503</v>
+      </c>
+      <c r="F26" s="32">
+        <v>40</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="39">
+        <v>3501</v>
+      </c>
+      <c r="F27" s="32">
+        <v>40</v>
+      </c>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" s="32">
+        <v>40</v>
+      </c>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="29">
+        <v>3560</v>
+      </c>
+      <c r="F37" s="66">
+        <v>20</v>
+      </c>
+      <c r="G37" s="81"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19">
+        <v>17092026</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" s="29">
+        <v>3558</v>
+      </c>
+      <c r="F38" s="66">
+        <v>40</v>
+      </c>
+      <c r="G38" s="81"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="81"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="81"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="81"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="81"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="81"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="81"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>9</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="81"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>10</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22:F29" xr:uid="{107D6956-A25D-430E-87AD-58F29C574C32}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17" xr:uid="{667C2021-4E48-4662-AC30-297C3003C15A}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4340,16 +6136,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4954,16 +6750,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5517,16 +7313,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6070,16 +7866,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6590,16 +8386,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7175,16 +8971,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7688,16 +9484,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7852,7 +9648,7 @@
       <c r="B13" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="69"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="18" t="s">
         <v>112</v>
       </c>
@@ -7889,10 +9685,10 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="69"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="24" t="s">
         <v>117</v>
       </c>
@@ -7908,8 +9704,8 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="69"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
       </c>
@@ -7925,8 +9721,8 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="69"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
       </c>
@@ -7942,8 +9738,8 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="69"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
       </c>
@@ -7959,7 +9755,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="66"/>
+      <c r="B19" s="73"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -7978,7 +9774,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="67"/>
+      <c r="B20" s="74"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -8063,7 +9859,7 @@
       <c r="B24" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="24" t="s">
         <v>139</v>
       </c>
@@ -8339,16 +10135,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8416,7 +10212,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="75" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -8437,7 +10233,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="64"/>
+      <c r="B10" s="75"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -8456,7 +10252,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="75" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -8479,7 +10275,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="64"/>
+      <c r="B12" s="75"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -8500,7 +10296,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="64"/>
+      <c r="B13" s="75"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -8521,7 +10317,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="64"/>
+      <c r="B14" s="75"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F18BBD0B-AB74-4608-8E25-5334F1B9C144}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A864E31D-A643-40B6-9B03-A618B3A509C4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,11 @@
     <sheet name="14-09" sheetId="11" r:id="rId11"/>
     <sheet name="15-09" sheetId="12" r:id="rId12"/>
     <sheet name="16-09" sheetId="13" r:id="rId13"/>
-    <sheet name="17-06" sheetId="14" r:id="rId14"/>
+    <sheet name="17-09" sheetId="14" r:id="rId14"/>
+    <sheet name="20-09" sheetId="15" r:id="rId15"/>
+    <sheet name="21-09" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="225">
   <si>
     <t>Date</t>
   </si>
@@ -708,6 +709,27 @@
   </si>
   <si>
     <t>500054 et 00679-525</t>
+  </si>
+  <si>
+    <t>ARKU855648 /7</t>
+  </si>
+  <si>
+    <t>B1779962</t>
+  </si>
+  <si>
+    <t>MSBU721115 /8</t>
+  </si>
+  <si>
+    <t>MSMU504541 /0</t>
+  </si>
+  <si>
+    <t>TCLU786835 /9</t>
+  </si>
+  <si>
+    <t>00533-508-31</t>
+  </si>
+  <si>
+    <t>018432-511-28</t>
   </si>
 </sst>
 </file>
@@ -718,7 +740,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -859,6 +881,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1101,7 +1130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1309,6 +1338,18 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1327,20 +1368,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1624,6 +1677,116 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69614840-93B2-4D83-AAAC-256EAF6D6EF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="514347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB8086D3-646C-4804-ADCA-9E3028476918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="533397"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2075,6 +2238,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -2705,25 +2872,43 @@
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46280</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
+        <v>46282</v>
+      </c>
+      <c r="B16" s="3">
+        <f>'17-09'!J1</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="3">
+        <f>'17-09'!J2</f>
+        <v>8</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" ref="D16" si="3">SUM(B16:C16)</f>
+        <v>8</v>
+      </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46281</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
+        <v>46285</v>
+      </c>
+      <c r="B17" s="3">
+        <f>'20-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <f>'20-09'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
+        <f t="shared" ref="D17" si="4">SUM(B17:C17)</f>
+        <v>2</v>
+      </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2732,7 +2917,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2741,7 +2926,7 @@
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2750,7 +2935,7 @@
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2779,11 +2964,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -2843,16 +3028,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3412,16 +3597,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3957,16 +4142,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4392,7 +4577,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="76" t="s">
+      <c r="G37" s="80" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4413,7 +4598,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="76"/>
+      <c r="G38" s="80"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -4432,7 +4617,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="76"/>
+      <c r="G39" s="80"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -4451,7 +4636,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="76"/>
+      <c r="G40" s="80"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -4472,7 +4657,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="76"/>
+      <c r="G41" s="80"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -4491,7 +4676,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="76"/>
+      <c r="G42" s="80"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -4510,7 +4695,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="76"/>
+      <c r="G43" s="80"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -4529,7 +4714,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="76"/>
+      <c r="G44" s="80"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -4548,7 +4733,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="76"/>
+      <c r="G45" s="80"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -4567,7 +4752,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="76"/>
+      <c r="G46" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4591,7 +4776,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477EFD95-392C-46D2-BEA6-1E5A8A7942D2}">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -4619,35 +4804,35 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B22:B36,"&lt;&gt;",C22:C36,"VH")</f>
+        <f>COUNTIFS(B22:B29,"&lt;&gt;",C22:C29,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C22:C41)-F2</f>
+        <f>COUNTA(C22:C33)-F2</f>
         <v>12</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E22:E36,"VIDE")</f>
+        <f>COUNTIF(E22:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4771,7 +4956,7 @@
       <c r="E16" s="24"/>
       <c r="F16" s="18"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>8</v>
       </c>
@@ -4781,7 +4966,7 @@
       <c r="E17" s="23"/>
       <c r="F17" s="18"/>
     </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="20"/>
       <c r="C18" s="7"/>
@@ -4790,13 +4975,13 @@
       <c r="F18" s="26"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="13"/>
       <c r="C20" s="7"/>
@@ -4804,7 +4989,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>10</v>
       </c>
@@ -4824,7 +5009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
         <v>1</v>
       </c>
@@ -4834,7 +5019,7 @@
       <c r="C22" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="D22" s="77" t="s">
+      <c r="D22" s="71" t="s">
         <v>184</v>
       </c>
       <c r="E22" s="39">
@@ -4844,7 +5029,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="25">
         <v>2</v>
       </c>
@@ -4854,7 +5039,7 @@
       <c r="C23" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="D23" s="71" t="s">
         <v>185</v>
       </c>
       <c r="E23" s="39">
@@ -4864,43 +5049,51 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="25">
         <v>3</v>
       </c>
       <c r="B24" s="19">
         <v>16092026</v>
       </c>
-      <c r="C24" s="27"/>
+      <c r="C24" s="27" t="s">
+        <v>206</v>
+      </c>
       <c r="D24" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E24" s="39">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="F24" s="32">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25">
         <v>4</v>
       </c>
       <c r="B25" s="19">
         <v>16092026</v>
       </c>
-      <c r="C25" s="27"/>
+      <c r="C25" s="29" t="s">
+        <v>203</v>
+      </c>
       <c r="D25" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E25" s="39">
-        <v>3563</v>
+        <v>3567</v>
       </c>
       <c r="F25" s="32">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25">
         <v>5</v>
       </c>
@@ -4908,37 +5101,47 @@
         <v>16092026</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E26" s="39">
-        <v>3565</v>
-      </c>
-      <c r="F26" s="32">
+        <v>3568</v>
+      </c>
+      <c r="F26" s="72">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25">
         <v>6</v>
       </c>
       <c r="B27" s="19">
         <v>16092026</v>
       </c>
-      <c r="C27" s="27"/>
+      <c r="C27" s="29" t="s">
+        <v>200</v>
+      </c>
       <c r="D27" s="24" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E27" s="39">
-        <v>3566</v>
+        <v>3570</v>
       </c>
       <c r="F27" s="32">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
         <v>7</v>
       </c>
@@ -4946,13 +5149,13 @@
         <v>16092026</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E28" s="39">
-        <v>3567</v>
+        <v>3502</v>
       </c>
       <c r="F28" s="32">
         <v>40</v>
@@ -4962,478 +5165,319 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
     </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="25">
         <v>8</v>
       </c>
       <c r="B29" s="19">
         <v>16092026</v>
       </c>
-      <c r="C29" s="27" t="s">
-        <v>204</v>
+      <c r="C29" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E29" s="39">
-        <v>3568</v>
-      </c>
-      <c r="F29" s="78">
+        <v>3580</v>
+      </c>
+      <c r="F29" s="32">
         <v>40</v>
       </c>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
       <c r="K29" s="31"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
         <v>9</v>
       </c>
       <c r="B30" s="19">
         <v>16092026</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="E30" s="39">
-        <v>3569</v>
-      </c>
-      <c r="F30" s="32">
-        <v>40</v>
-      </c>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
+      <c r="C30" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="D30" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="E30" s="29">
+        <v>3554</v>
+      </c>
+      <c r="F30" s="66">
+        <v>20</v>
+      </c>
       <c r="K30" s="31"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25">
         <v>10</v>
       </c>
       <c r="B31" s="19">
         <v>16092026</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="39">
-        <v>3570</v>
-      </c>
-      <c r="F31" s="32">
-        <v>40</v>
-      </c>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
+      <c r="C31" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D31" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="29">
+        <v>0</v>
+      </c>
+      <c r="F31" s="66" t="s">
+        <v>157</v>
+      </c>
       <c r="K31" s="31"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25">
         <v>11</v>
       </c>
       <c r="B32" s="19">
         <v>16092026</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32" s="39">
-        <v>3503</v>
-      </c>
-      <c r="F32" s="32">
-        <v>40</v>
-      </c>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" s="29">
+        <v>0</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="25">
         <v>12</v>
       </c>
       <c r="B33" s="19">
         <v>16092026</v>
       </c>
-      <c r="C33" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="E33" s="39">
-        <v>3502</v>
-      </c>
-      <c r="F33" s="32">
-        <v>40</v>
-      </c>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
+      <c r="C33" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" s="25">
+        <v>3943</v>
+      </c>
+      <c r="F33" s="73">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="81"/>
+      <c r="B34" s="82"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="85"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="39">
-        <v>3501</v>
-      </c>
-      <c r="F34" s="32">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="25">
-        <v>14</v>
-      </c>
-      <c r="B35" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="32">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="25">
+      <c r="D37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="E36" s="39">
-        <v>3580</v>
-      </c>
-      <c r="F36" s="32">
-        <v>40</v>
-      </c>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="25">
-        <v>16</v>
-      </c>
-      <c r="B37" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C37" s="33"/>
-      <c r="D37" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="E37" s="24"/>
-      <c r="F37" s="32">
-        <v>40</v>
-      </c>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B38" s="19">
         <v>16092026</v>
       </c>
-      <c r="C38" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="65" t="s">
-        <v>153</v>
+      <c r="C38" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>101</v>
       </c>
       <c r="E38" s="29">
-        <v>3554</v>
+        <v>3556</v>
       </c>
       <c r="F38" s="66">
-        <v>20</v>
-      </c>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="G38" s="80"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B39" s="19">
         <v>16092026</v>
       </c>
-      <c r="C39" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="67" t="s">
-        <v>155</v>
+      <c r="C39" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>51</v>
       </c>
       <c r="E39" s="29">
-        <v>0</v>
-      </c>
-      <c r="F39" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3555</v>
+      </c>
+      <c r="F39" s="18">
+        <v>40</v>
+      </c>
+      <c r="G39" s="80"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B40" s="19">
         <v>16092026</v>
       </c>
-      <c r="C40" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="D40" s="66" t="s">
-        <v>158</v>
+      <c r="C40" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="34">
+        <v>18233786</v>
       </c>
       <c r="E40" s="29">
-        <v>0</v>
-      </c>
-      <c r="F40" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3558</v>
+      </c>
+      <c r="F40" s="66">
+        <v>40</v>
+      </c>
+      <c r="G40" s="80"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
-        <v>20</v>
-      </c>
-      <c r="B41" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="E41" s="25">
-        <v>3943</v>
-      </c>
-      <c r="F41" s="80">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="80"/>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="80"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="80"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>7</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="80"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>8</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="80"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>9</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="80"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
         <v>10</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>1</v>
-      </c>
-      <c r="B45" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" s="29">
-        <v>3556</v>
-      </c>
-      <c r="F45" s="66">
-        <v>40</v>
-      </c>
-      <c r="G45" s="76"/>
-    </row>
-    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
-        <v>2</v>
-      </c>
-      <c r="B46" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C46" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="29">
-        <v>3555</v>
-      </c>
-      <c r="F46" s="18">
-        <v>40</v>
-      </c>
-      <c r="G46" s="76"/>
-    </row>
-    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="25">
-        <v>3</v>
-      </c>
-      <c r="B47" s="19">
-        <v>16092026</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" s="34">
-        <v>18233786</v>
-      </c>
-      <c r="E47" s="29">
-        <v>3558</v>
-      </c>
-      <c r="F47" s="66">
-        <v>40</v>
-      </c>
-      <c r="G47" s="76"/>
-    </row>
-    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="25">
-        <v>4</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="76"/>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="25">
-        <v>5</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="76"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="25">
-        <v>6</v>
-      </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="76"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="25">
-        <v>7</v>
-      </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="76"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="25">
-        <v>8</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="76"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="25">
-        <v>9</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="76"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="25">
-        <v>10</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="76"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="G45:G54"/>
+    <mergeCell ref="G38:G47"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22:F37" xr:uid="{891C7987-B10E-436C-8334-E349696CE1DC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22:F29" xr:uid="{891C7987-B10E-436C-8334-E349696CE1DC}">
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F45:F47 F8:F17 F38:F40" xr:uid="{43175F8C-86E7-45FE-A167-E0EFC0821C3A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F40 F8:F17 F30:F32" xr:uid="{43175F8C-86E7-45FE-A167-E0EFC0821C3A}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5454,53 +5498,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="H1" s="8">
+      <c r="J1" s="8">
         <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="F2" s="8">
+      <c r="H2" s="8">
         <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
         <v>0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8">
-        <f>COUNTA(C22:C31)-F2</f>
+      <c r="J2" s="8">
+        <f>COUNTA(C22:C31)-H2</f>
         <v>8</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="10">
+      <c r="L2" s="10">
         <f>COUNTIF(E22:E31,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-    </row>
-    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -5509,11 +5553,11 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -5533,7 +5577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -5543,7 +5587,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -5553,7 +5597,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -5563,7 +5607,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -5573,7 +5617,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -5583,7 +5627,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -5593,7 +5637,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -5603,7 +5647,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="53"/>
       <c r="C15" s="68"/>
@@ -5611,7 +5655,7 @@
       <c r="E15" s="24"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="53"/>
       <c r="C16" s="68"/>
@@ -5830,6 +5874,9 @@
       <c r="D28" s="24" t="s">
         <v>199</v>
       </c>
+      <c r="E28" s="24" t="s">
+        <v>157</v>
+      </c>
       <c r="F28" s="32">
         <v>40</v>
       </c>
@@ -5852,7 +5899,9 @@
       <c r="D29" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="24"/>
+      <c r="E29" s="24" t="s">
+        <v>157</v>
+      </c>
       <c r="F29" s="32">
         <v>40</v>
       </c>
@@ -5958,7 +6007,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="81"/>
+      <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
@@ -5979,7 +6028,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="81"/>
+      <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5990,7 +6039,7 @@
       <c r="D39" s="46"/>
       <c r="E39" s="29"/>
       <c r="F39" s="66"/>
-      <c r="G39" s="81"/>
+      <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -6001,7 +6050,7 @@
       <c r="D40" s="46"/>
       <c r="E40" s="29"/>
       <c r="F40" s="39"/>
-      <c r="G40" s="81"/>
+      <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -6012,7 +6061,7 @@
       <c r="D41" s="29"/>
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
-      <c r="G41" s="81"/>
+      <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -6023,7 +6072,7 @@
       <c r="D42" s="46"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="81"/>
+      <c r="G42" s="74"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -6034,7 +6083,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="81"/>
+      <c r="G43" s="74"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -6045,7 +6094,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="81"/>
+      <c r="G44" s="74"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -6056,7 +6105,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="81"/>
+      <c r="G45" s="74"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -6067,7 +6116,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="81"/>
+      <c r="G46" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6078,6 +6127,1184 @@
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17" xr:uid="{667C2021-4E48-4662-AC30-297C3003C15A}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB353A5-9210-4845-B819-E6D5BC671F07}">
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="39">
+        <v>3556</v>
+      </c>
+      <c r="F22" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="29">
+        <v>3555</v>
+      </c>
+      <c r="F23" s="18">
+        <v>40</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="32"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="32"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="32"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="32"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="F28" s="32"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="32"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C37" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="87" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="88">
+        <v>3656</v>
+      </c>
+      <c r="F37" s="18">
+        <v>40</v>
+      </c>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C38" s="89" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="87" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="88">
+        <v>3657</v>
+      </c>
+      <c r="F38" s="18">
+        <v>40</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="46"/>
+      <c r="E39" s="29">
+        <v>3660</v>
+      </c>
+      <c r="F39" s="66">
+        <v>40</v>
+      </c>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="D40" s="86"/>
+      <c r="E40" s="29">
+        <v>3659</v>
+      </c>
+      <c r="F40" s="39">
+        <v>40</v>
+      </c>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19">
+        <v>20092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29">
+        <v>3658</v>
+      </c>
+      <c r="F41" s="29">
+        <v>40</v>
+      </c>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>9</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>10</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17 F23" xr:uid="{8C6CB5B7-B1F5-4A45-891F-E684958B2DD2}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22 F24:F29" xr:uid="{2CCF6909-05FE-4DA8-96D3-1096910950B3}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26A801C-07E7-402B-ABC9-BF70D8606522}">
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="J1" s="8">
+        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="H2" s="8">
+        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8">
+        <f>COUNTA(C22:C31)-H2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10">
+        <f>COUNTIF(E22:E31,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>8</v>
+      </c>
+      <c r="B17" s="42"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>1</v>
+      </c>
+      <c r="B22" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C22" s="34"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="32"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>2</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="18"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>3</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="32"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="32"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="32"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>6</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="32"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>7</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="24"/>
+      <c r="F28" s="32"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>8</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="32"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>9</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>10</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="25"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>11</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="25"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>1</v>
+      </c>
+      <c r="B37" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>2</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>5</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>6</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>7</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>8</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>9</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>10</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22 F24:F29" xr:uid="{314564C8-73C4-4FE1-B1A4-E2956228C86B}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17 F23" xr:uid="{E43818B9-96C6-4529-B8DF-B4F7D161AD53}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6136,16 +7363,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6750,16 +7977,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7313,16 +8540,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7866,16 +9093,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8386,16 +9613,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8971,16 +10198,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9484,16 +10711,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9685,7 +10912,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="76" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -9704,7 +10931,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="73"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -9721,7 +10948,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="73"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -9738,7 +10965,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="73"/>
+      <c r="B18" s="77"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -9755,7 +10982,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="73"/>
+      <c r="B19" s="77"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -9774,7 +11001,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="74"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -10135,16 +11362,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10212,7 +11439,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="79" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -10233,7 +11460,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="75"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -10252,7 +11479,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="79" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -10275,7 +11502,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="75"/>
+      <c r="B12" s="79"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -10296,7 +11523,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="75"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -10317,7 +11544,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="75"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A864E31D-A643-40B6-9B03-A618B3A509C4}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0E0758E-3E6C-4707-94EE-34898817A289}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="16" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="17-09" sheetId="14" r:id="rId14"/>
     <sheet name="20-09" sheetId="15" r:id="rId15"/>
     <sheet name="21-09" sheetId="16" r:id="rId16"/>
+    <sheet name="22-09" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="256">
   <si>
     <t>Date</t>
   </si>
@@ -730,6 +731,99 @@
   </si>
   <si>
     <t>018432-511-28</t>
+  </si>
+  <si>
+    <t>MBSU281340 /6</t>
+  </si>
+  <si>
+    <t>LB0263265</t>
+  </si>
+  <si>
+    <t>00018-506-31</t>
+  </si>
+  <si>
+    <t>00099-509-31</t>
+  </si>
+  <si>
+    <t>00328-507-31</t>
+  </si>
+  <si>
+    <t>ARKU241132 /0</t>
+  </si>
+  <si>
+    <t>TRHU307416 /1</t>
+  </si>
+  <si>
+    <t>MSNU191236 /9</t>
+  </si>
+  <si>
+    <t>SK360769</t>
+  </si>
+  <si>
+    <t>B1758829</t>
+  </si>
+  <si>
+    <t>B1758825</t>
+  </si>
+  <si>
+    <t>FSCU873148 /5</t>
+  </si>
+  <si>
+    <t>HASU512425 /3</t>
+  </si>
+  <si>
+    <t>CMAU789256 /2</t>
+  </si>
+  <si>
+    <t>MRKU753756 /7</t>
+  </si>
+  <si>
+    <t>ML-IN2987561</t>
+  </si>
+  <si>
+    <t>MRKU772089 /7</t>
+  </si>
+  <si>
+    <t>ML-IN2987565</t>
+  </si>
+  <si>
+    <t>MRKU905919 /5</t>
+  </si>
+  <si>
+    <t>ML-IN2987562</t>
+  </si>
+  <si>
+    <t>MRSU023326 /7</t>
+  </si>
+  <si>
+    <t>ML-IN2987566</t>
+  </si>
+  <si>
+    <t>MSKU704341 /6</t>
+  </si>
+  <si>
+    <t>ML-IN2987564</t>
+  </si>
+  <si>
+    <t>MSKU730475 /7</t>
+  </si>
+  <si>
+    <t>ML-IN2987563</t>
+  </si>
+  <si>
+    <t>00117-523-31</t>
+  </si>
+  <si>
+    <t>500017-525-31</t>
+  </si>
+  <si>
+    <t>00139-525-31</t>
+  </si>
+  <si>
+    <t>000164-513-31</t>
+  </si>
+  <si>
+    <t>HLXU629565 /7</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1350,6 +1444,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1368,32 +1477,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1787,6 +1875,61 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="533397"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBC85AFE-D9D1-4696-BD71-50DB4C1158F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="552447"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2875,11 +3018,11 @@
         <v>46282</v>
       </c>
       <c r="B16" s="3">
-        <f>'17-09'!J1</f>
+        <f>'17-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>'17-09'!J2</f>
+        <f>'17-09'!H2</f>
         <v>8</v>
       </c>
       <c r="D16" s="4">
@@ -2910,18 +3053,36 @@
       <c r="A18" s="2">
         <v>46286</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
+      <c r="B18" s="3">
+        <f>'21-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <f>'21-09'!H2</f>
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <f t="shared" ref="D18" si="5">SUM(B18:C18)</f>
+        <v>4</v>
+      </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46287</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="3">
+        <f>'22-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="3">
+        <f>'22-09'!H2</f>
+        <v>7</v>
+      </c>
+      <c r="D19" s="4">
+        <f t="shared" ref="D19" si="6">SUM(B19:C19)</f>
+        <v>7</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -2944,7 +3105,7 @@
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46286</v>
+        <v>46292</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2952,6 +3113,12 @@
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>46293</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -2964,11 +3131,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3028,16 +3195,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3597,16 +3764,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4142,16 +4309,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4577,7 +4744,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="80" t="s">
+      <c r="G37" s="85" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4598,7 +4765,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="80"/>
+      <c r="G38" s="85"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -4617,7 +4784,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="80"/>
+      <c r="G39" s="85"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -4636,7 +4803,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="80"/>
+      <c r="G40" s="85"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -4657,7 +4824,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="80"/>
+      <c r="G41" s="85"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -4676,7 +4843,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="80"/>
+      <c r="G42" s="85"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -4695,7 +4862,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="80"/>
+      <c r="G43" s="85"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -4714,7 +4881,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="80"/>
+      <c r="G44" s="85"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -4733,7 +4900,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="80"/>
+      <c r="G45" s="85"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -4752,7 +4919,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="80"/>
+      <c r="G46" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4823,16 +4990,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5278,12 +5445,12 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="81"/>
-      <c r="B34" s="82"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="84"/>
-      <c r="E34" s="81"/>
-      <c r="F34" s="85"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="41"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
@@ -5340,7 +5507,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="80"/>
+      <c r="G38" s="85"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5361,7 +5528,7 @@
       <c r="F39" s="18">
         <v>40</v>
       </c>
-      <c r="G39" s="80"/>
+      <c r="G39" s="85"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5382,7 +5549,7 @@
       <c r="F40" s="66">
         <v>40</v>
       </c>
-      <c r="G40" s="80"/>
+      <c r="G40" s="85"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5393,7 +5560,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="39"/>
-      <c r="G41" s="80"/>
+      <c r="G41" s="85"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5404,7 +5571,7 @@
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="80"/>
+      <c r="G42" s="85"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -5415,7 +5582,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="80"/>
+      <c r="G43" s="85"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -5426,7 +5593,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="80"/>
+      <c r="G44" s="85"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -5437,7 +5604,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="80"/>
+      <c r="G45" s="85"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5448,7 +5615,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="80"/>
+      <c r="G46" s="85"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
@@ -5459,7 +5626,7 @@
       <c r="D47" s="46"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="80"/>
+      <c r="G47" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5498,53 +5665,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
+      <c r="H1" s="8">
         <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="H2" s="8">
+      <c r="F2" s="8">
         <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
         <v>0</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C22:C31)-F2</f>
+        <v>8</v>
+      </c>
       <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C22:C31)-H2</f>
-        <v>8</v>
-      </c>
-      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="J2" s="10">
         <f>COUNTIF(E22:E31,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -5553,11 +5720,11 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -5577,7 +5744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -5587,7 +5754,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -5597,7 +5764,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -5607,7 +5774,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -5617,7 +5784,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -5627,7 +5794,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -5637,7 +5804,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -5647,7 +5814,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="53"/>
       <c r="C15" s="68"/>
@@ -5655,7 +5822,7 @@
       <c r="E15" s="24"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="53"/>
       <c r="C16" s="68"/>
@@ -6186,16 +6353,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6590,13 +6757,13 @@
       <c r="B37" s="19">
         <v>20092026</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="87" t="s">
+      <c r="D37" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="E37" s="88">
+      <c r="E37" s="78">
         <v>3656</v>
       </c>
       <c r="F37" s="18">
@@ -6611,13 +6778,13 @@
       <c r="B38" s="19">
         <v>20092026</v>
       </c>
-      <c r="C38" s="89" t="s">
+      <c r="C38" s="79" t="s">
         <v>218</v>
       </c>
-      <c r="D38" s="87" t="s">
+      <c r="D38" s="77" t="s">
         <v>219</v>
       </c>
-      <c r="E38" s="88">
+      <c r="E38" s="78">
         <v>3657</v>
       </c>
       <c r="F38" s="18">
@@ -6654,7 +6821,7 @@
       <c r="C40" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="86"/>
+      <c r="D40" s="76"/>
       <c r="E40" s="29">
         <v>3659</v>
       </c>
@@ -6758,7 +6925,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26A801C-07E7-402B-ABC9-BF70D8606522}">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -6773,53 +6940,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
-        <f>COUNTIF(C8:C17,"&lt;&gt;")</f>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
       <c r="H2" s="8">
-        <f>COUNTIFS(B22:B31,"&lt;&gt;",C22:C31,"VH")</f>
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>4</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C22:C31)-H2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="10">
-        <f>COUNTIF(E22:E31,"VIDE")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -6828,11 +6995,11 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -6852,7 +7019,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -6862,7 +7029,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -6872,7 +7039,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -6882,7 +7049,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -6892,7 +7059,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -6902,7 +7069,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -6912,7 +7079,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -6922,96 +7089,148 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="53"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
       <c r="C15" s="68"/>
       <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="18"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
-        <v>8</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
-      <c r="B18" s="20"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D19" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F19" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="39">
+        <v>3558</v>
+      </c>
+      <c r="F20" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="29">
+        <v>3660</v>
+      </c>
+      <c r="F21" s="66">
+        <v>40</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" s="19">
         <v>21092026</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="32"/>
+      <c r="C22" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3659</v>
+      </c>
+      <c r="F22" s="39">
+        <v>40</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25">
-        <v>2</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="29">
+        <v>3658</v>
+      </c>
+      <c r="F23" s="29">
+        <v>40</v>
+      </c>
       <c r="I23" s="31"/>
       <c r="J23" s="31"/>
       <c r="K23" s="31"/>
@@ -7020,10 +7239,10 @@
     </row>
     <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B24" s="19"/>
-      <c r="C24" s="27"/>
+      <c r="C24" s="29"/>
       <c r="D24" s="24"/>
       <c r="E24" s="39"/>
       <c r="F24" s="32"/>
@@ -7035,10 +7254,10 @@
     </row>
     <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="29"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="24"/>
       <c r="E25" s="39"/>
       <c r="F25" s="32"/>
@@ -7050,12 +7269,11 @@
     </row>
     <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="29"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="39"/>
       <c r="F26" s="32"/>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
@@ -7063,187 +7281,198 @@
       <c r="L26" s="31"/>
       <c r="M26" s="31"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="27"/>
       <c r="D27" s="24"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="32"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B28" s="19"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="24"/>
-      <c r="F28" s="32"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="32"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
       <c r="E30" s="30"/>
       <c r="F30" s="25"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="25">
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="25"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25">
-        <v>11</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="25"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="35"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="15" t="s">
+      <c r="B34" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D34" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E34" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F34" s="16" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="E35" s="86">
+        <v>3655</v>
+      </c>
+      <c r="F35" s="18">
+        <v>20</v>
+      </c>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>21092026</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="29">
+        <v>239388</v>
+      </c>
+      <c r="E36" s="29">
+        <v>3559</v>
+      </c>
+      <c r="F36" s="18">
+        <v>40</v>
+      </c>
+      <c r="G36" s="74"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25">
-        <v>1</v>
-      </c>
-      <c r="B37" s="19">
-        <v>21092026</v>
-      </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="18"/>
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="66"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="87"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="39"/>
       <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="34"/>
-      <c r="D39" s="46"/>
+      <c r="D39" s="29"/>
       <c r="E39" s="29"/>
-      <c r="F39" s="66"/>
+      <c r="F39" s="29"/>
       <c r="G39" s="74"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="46"/>
       <c r="E40" s="29"/>
-      <c r="F40" s="39"/>
+      <c r="F40" s="29"/>
       <c r="G40" s="74"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="34"/>
-      <c r="D41" s="29"/>
+      <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="29"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="34"/>
@@ -7254,7 +7483,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="34"/>
@@ -7265,7 +7494,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="34"/>
@@ -7274,39 +7503,720 @@
       <c r="F44" s="29"/>
       <c r="G44" s="74"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>9</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="74"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
-        <v>10</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="74"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18 F22 F24:F29" xr:uid="{314564C8-73C4-4FE1-B1A4-E2956228C86B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F20 F24:F27" xr:uid="{314564C8-73C4-4FE1-B1A4-E2956228C86B}">
       <formula1>"20,40,45,50"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F37:F39 F8:F17 F23" xr:uid="{E43818B9-96C6-4529-B8DF-B4F7D161AD53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F37 F21 F8:F15" xr:uid="{E43818B9-96C6-4529-B8DF-B4F7D161AD53}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E6184E-8A55-4168-8E2F-3007313C04E4}">
+  <dimension ref="A1:T44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18"/>
+      <c r="T18"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F20" s="18">
+        <v>20</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="87"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="F21" s="18">
+        <v>20</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="18">
+        <v>20</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="18">
+        <v>20</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" s="18">
+        <v>20</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="18">
+        <v>20</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="86">
+        <v>3559</v>
+      </c>
+      <c r="F26" s="32">
+        <v>40</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="32"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="28"/>
+      <c r="E35" s="86">
+        <v>3701</v>
+      </c>
+      <c r="F35" s="18">
+        <v>40</v>
+      </c>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29">
+        <v>3702</v>
+      </c>
+      <c r="F36" s="18">
+        <v>40</v>
+      </c>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="29">
+        <v>3703</v>
+      </c>
+      <c r="F37" s="18">
+        <v>40</v>
+      </c>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="29">
+        <v>3652</v>
+      </c>
+      <c r="F38" s="39">
+        <v>20</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" s="29">
+        <v>3653</v>
+      </c>
+      <c r="F39" s="29">
+        <v>20</v>
+      </c>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="29">
+        <v>3654</v>
+      </c>
+      <c r="F40" s="29">
+        <v>20</v>
+      </c>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="29">
+        <v>3651</v>
+      </c>
+      <c r="F41" s="29">
+        <v>40</v>
+      </c>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>8</v>
+      </c>
+      <c r="B42" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29">
+        <v>3711</v>
+      </c>
+      <c r="F42" s="29">
+        <v>20</v>
+      </c>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>9</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>10</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F37 F8:F15 F20:F25" xr:uid="{C3462CE8-8B3A-4838-AE1A-E8D51F80F098}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F26:F27" xr:uid="{A9875B32-7784-4A44-B6FD-4CB069812067}">
+      <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7363,16 +8273,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7977,16 +8887,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8540,16 +9450,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9093,16 +10003,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9613,16 +10523,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10198,16 +11108,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10711,16 +11621,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10912,7 +11822,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="81" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -10931,7 +11841,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -10948,7 +11858,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -10965,7 +11875,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="77"/>
+      <c r="B18" s="82"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -10982,7 +11892,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="77"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -11001,7 +11911,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="78"/>
+      <c r="B20" s="83"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -11362,16 +12272,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11439,7 +12349,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="84" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -11460,7 +12370,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="79"/>
+      <c r="B10" s="84"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -11479,7 +12389,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="84" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -11502,7 +12412,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="79"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -11523,7 +12433,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="79"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -11544,7 +12454,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="79"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0E0758E-3E6C-4707-94EE-34898817A289}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD6975D4-EBD5-42EE-AA6D-EC0E99933B22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="16" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="16" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="20-09" sheetId="15" r:id="rId15"/>
     <sheet name="21-09" sheetId="16" r:id="rId16"/>
     <sheet name="22-09" sheetId="17" r:id="rId17"/>
+    <sheet name="23-09" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="257">
   <si>
     <t>Date</t>
   </si>
@@ -824,6 +825,9 @@
   </si>
   <si>
     <t>HLXU629565 /7</t>
+  </si>
+  <si>
+    <t>00378-516-31</t>
   </si>
 </sst>
 </file>
@@ -965,11 +969,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1459,6 +1465,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1476,12 +1488,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1930,6 +1936,61 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="552447"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDD50CFF-FF1F-4F3B-9A82-7E82108F67F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="571497"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3072,16 +3133,16 @@
         <v>46287</v>
       </c>
       <c r="B19" s="3">
-        <f>'22-09'!H1</f>
+        <f>'22-09'!J1</f>
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>'22-09'!H2</f>
-        <v>7</v>
+        <f>'22-09'!J2</f>
+        <v>8</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" ref="D19" si="6">SUM(B19:C19)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -3131,11 +3192,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C22)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D22)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3195,16 +3256,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3764,16 +3825,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4309,16 +4370,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4744,7 +4805,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="85" t="s">
+      <c r="G37" s="87" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4765,7 +4826,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="85"/>
+      <c r="G38" s="87"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -4784,7 +4845,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="85"/>
+      <c r="G39" s="87"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -4803,7 +4864,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="85"/>
+      <c r="G40" s="87"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -4824,7 +4885,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="85"/>
+      <c r="G41" s="87"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -4843,7 +4904,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="85"/>
+      <c r="G42" s="87"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -4862,7 +4923,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="85"/>
+      <c r="G43" s="87"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -4881,7 +4942,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="85"/>
+      <c r="G44" s="87"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -4900,7 +4961,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="85"/>
+      <c r="G45" s="87"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -4919,7 +4980,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="85"/>
+      <c r="G46" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4990,16 +5051,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5507,7 +5568,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="85"/>
+      <c r="G38" s="87"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5528,7 +5589,7 @@
       <c r="F39" s="18">
         <v>40</v>
       </c>
-      <c r="G39" s="85"/>
+      <c r="G39" s="87"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5549,7 +5610,7 @@
       <c r="F40" s="66">
         <v>40</v>
       </c>
-      <c r="G40" s="85"/>
+      <c r="G40" s="87"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5560,7 +5621,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="39"/>
-      <c r="G41" s="85"/>
+      <c r="G41" s="87"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5571,7 +5632,7 @@
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="85"/>
+      <c r="G42" s="87"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -5582,7 +5643,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="85"/>
+      <c r="G43" s="87"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -5593,7 +5654,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="85"/>
+      <c r="G44" s="87"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -5604,7 +5665,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="85"/>
+      <c r="G45" s="87"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5615,7 +5676,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="85"/>
+      <c r="G46" s="87"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
@@ -5626,7 +5687,7 @@
       <c r="D47" s="46"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="85"/>
+      <c r="G47" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5697,16 +5758,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6353,16 +6414,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6972,16 +7033,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7386,7 +7447,7 @@
       <c r="D35" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="E35" s="86">
+      <c r="E35" s="80">
         <v>3655</v>
       </c>
       <c r="F35" s="18">
@@ -7539,53 +7600,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="H1" s="8">
+      <c r="J1" s="8">
         <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="F2" s="8">
+      <c r="H2" s="8">
         <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
         <v>0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8">
-        <f>COUNTA(C20:C29)-F2</f>
-        <v>7</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="8">
+        <f>COUNTA(C20:C29)-H2</f>
+        <v>8</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="10">
+      <c r="L2" s="10">
         <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-    </row>
-    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -7594,11 +7655,11 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
         <v>10</v>
       </c>
@@ -7618,7 +7679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -7628,7 +7689,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -7638,7 +7699,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -7648,7 +7709,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -7658,7 +7719,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -7668,7 +7729,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -7678,7 +7739,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -7688,7 +7749,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
@@ -7698,7 +7759,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="20"/>
       <c r="C16" s="7"/>
@@ -7749,7 +7810,7 @@
       </c>
       <c r="N19" s="31"/>
       <c r="O19" s="31"/>
-      <c r="P19" s="87"/>
+      <c r="P19" s="81"/>
       <c r="Q19" s="31"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
@@ -7775,7 +7836,7 @@
         <v>20</v>
       </c>
       <c r="N20" s="31"/>
-      <c r="O20" s="87"/>
+      <c r="O20" s="81"/>
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
       <c r="R20"/>
@@ -7920,7 +7981,7 @@
       <c r="D26" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="86">
+      <c r="E26" s="80">
         <v>3559</v>
       </c>
       <c r="F26" s="32">
@@ -7936,11 +7997,21 @@
       <c r="A27" s="25">
         <v>8</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="32"/>
+      <c r="B27" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="24">
+        <v>3657</v>
+      </c>
+      <c r="F27" s="32">
+        <v>40</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
@@ -8035,7 +8106,7 @@
         <v>236</v>
       </c>
       <c r="D35" s="28"/>
-      <c r="E35" s="86">
+      <c r="E35" s="80">
         <v>3701</v>
       </c>
       <c r="F35" s="18">
@@ -8217,6 +8288,719 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F26:F27" xr:uid="{A9875B32-7784-4A44-B6FD-4CB069812067}">
       <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC21F363-DF41-4D97-B1E8-59137C43A9C5}">
+  <dimension ref="A1:T44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>8</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18"/>
+      <c r="T18"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F20" s="18">
+        <v>20</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="F21" s="18">
+        <v>20</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="18">
+        <v>20</v>
+      </c>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="18">
+        <v>20</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" s="18">
+        <v>20</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="18">
+        <v>20</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="80">
+        <v>3559</v>
+      </c>
+      <c r="F26" s="32">
+        <v>40</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="E27" s="24">
+        <v>3657</v>
+      </c>
+      <c r="F27" s="32">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="28"/>
+      <c r="E35" s="80">
+        <v>3701</v>
+      </c>
+      <c r="F35" s="18">
+        <v>40</v>
+      </c>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29">
+        <v>3702</v>
+      </c>
+      <c r="F36" s="18">
+        <v>40</v>
+      </c>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="29">
+        <v>3703</v>
+      </c>
+      <c r="F37" s="18">
+        <v>40</v>
+      </c>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C38" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="29">
+        <v>3652</v>
+      </c>
+      <c r="F38" s="39">
+        <v>20</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" s="29">
+        <v>3653</v>
+      </c>
+      <c r="F39" s="29">
+        <v>20</v>
+      </c>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="29">
+        <v>3654</v>
+      </c>
+      <c r="F40" s="29">
+        <v>20</v>
+      </c>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="29">
+        <v>3651</v>
+      </c>
+      <c r="F41" s="29">
+        <v>40</v>
+      </c>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>8</v>
+      </c>
+      <c r="B42" s="19">
+        <v>22092026</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29">
+        <v>3711</v>
+      </c>
+      <c r="F42" s="29">
+        <v>20</v>
+      </c>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>9</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>10</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F26:F27" xr:uid="{D0CD690B-E68F-48FC-A110-B334FF72DAC3}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F37 F8:F15 F20:F25" xr:uid="{716D21BA-24B1-40B3-B493-FD2632C7794E}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8273,16 +9057,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8887,16 +9671,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9450,16 +10234,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10003,16 +10787,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10523,16 +11307,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11108,16 +11892,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11621,16 +12405,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11822,7 +12606,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="83" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -11841,7 +12625,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -11858,7 +12642,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="82"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -11875,7 +12659,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="82"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -11892,7 +12676,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="82"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -11911,7 +12695,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="83"/>
+      <c r="B20" s="85"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -12272,16 +13056,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12349,7 +13133,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="86" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -12370,7 +13154,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="84"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -12389,7 +13173,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="86" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -12412,7 +13196,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="84"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -12433,7 +13217,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="84"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -12454,7 +13238,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="84"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD6975D4-EBD5-42EE-AA6D-EC0E99933B22}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BAE2EE8-6EE0-47EF-AACD-9589BF30D51C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="16" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="257">
   <si>
     <t>Date</t>
   </si>
@@ -3133,11 +3133,11 @@
         <v>46287</v>
       </c>
       <c r="B19" s="3">
-        <f>'22-09'!J1</f>
+        <f>'22-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>'22-09'!J2</f>
+        <f>'22-09'!H2</f>
         <v>8</v>
       </c>
       <c r="D19" s="4">
@@ -3150,9 +3150,18 @@
       <c r="A20" s="2">
         <v>46288</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
+      <c r="B20" s="3">
+        <f>'23-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="3">
+        <f>'23-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" ref="D20" si="7">SUM(B20:C20)</f>
+        <v>0</v>
+      </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -7600,38 +7609,38 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
+      <c r="H1" s="8">
         <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="H2" s="8">
+      <c r="F2" s="8">
         <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
         <v>0</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>8</v>
+      </c>
       <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C20:C29)-H2</f>
-        <v>8</v>
-      </c>
-      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="J2" s="10">
         <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="82" t="s">
         <v>8</v>
       </c>
@@ -7643,10 +7652,10 @@
       <c r="G3" s="82"/>
       <c r="H3" s="82"/>
     </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -7655,11 +7664,11 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
         <v>10</v>
       </c>
@@ -7679,7 +7688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -7689,7 +7698,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -7699,7 +7708,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -7709,7 +7718,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -7719,7 +7728,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -7729,7 +7738,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -7739,7 +7748,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -7749,7 +7758,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
@@ -7759,7 +7768,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="20"/>
       <c r="C16" s="7"/>
@@ -8334,7 +8343,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C20:C29)-F2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -8533,21 +8542,11 @@
       <c r="A20" s="25">
         <v>1</v>
       </c>
-      <c r="B20" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="F20" s="18">
-        <v>20</v>
-      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="N20" s="31"/>
       <c r="O20" s="81"/>
       <c r="P20" s="31"/>
@@ -8560,21 +8559,11 @@
       <c r="A21" s="25">
         <v>2</v>
       </c>
-      <c r="B21" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="F21" s="18">
-        <v>20</v>
-      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
       <c r="K21" s="31"/>
@@ -8585,21 +8574,11 @@
       <c r="A22" s="25">
         <v>3</v>
       </c>
-      <c r="B22" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="F22" s="18">
-        <v>20</v>
-      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="18"/>
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
       <c r="K22" s="31"/>
@@ -8610,21 +8589,11 @@
       <c r="A23" s="25">
         <v>4</v>
       </c>
-      <c r="B23" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F23" s="18">
-        <v>20</v>
-      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="18"/>
       <c r="I23" s="31"/>
       <c r="J23" s="31"/>
       <c r="K23" s="31"/>
@@ -8635,21 +8604,11 @@
       <c r="A24" s="25">
         <v>5</v>
       </c>
-      <c r="B24" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="F24" s="18">
-        <v>20</v>
-      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="18"/>
       <c r="I24" s="31"/>
       <c r="J24" s="31"/>
       <c r="K24" s="31"/>
@@ -8660,21 +8619,11 @@
       <c r="A25" s="25">
         <v>6</v>
       </c>
-      <c r="B25" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="F25" s="18">
-        <v>20</v>
-      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="18"/>
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
       <c r="K25" s="31"/>
@@ -8685,21 +8634,11 @@
       <c r="A26" s="25">
         <v>7</v>
       </c>
-      <c r="B26" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" s="80">
-        <v>3559</v>
-      </c>
-      <c r="F26" s="32">
-        <v>40</v>
-      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="32"/>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
@@ -8710,21 +8649,11 @@
       <c r="A27" s="25">
         <v>8</v>
       </c>
-      <c r="B27" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E27" s="24">
-        <v>3657</v>
-      </c>
-      <c r="F27" s="32">
-        <v>40</v>
-      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="32"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
@@ -8812,160 +8741,88 @@
       <c r="A35" s="25">
         <v>1</v>
       </c>
-      <c r="B35" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>236</v>
-      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="28"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="80">
-        <v>3701</v>
-      </c>
-      <c r="F35" s="18">
-        <v>40</v>
-      </c>
+      <c r="E35" s="80"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
         <v>2</v>
       </c>
-      <c r="B36" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>237</v>
-      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
       <c r="D36" s="29"/>
-      <c r="E36" s="29">
-        <v>3702</v>
-      </c>
-      <c r="F36" s="18">
-        <v>40</v>
-      </c>
+      <c r="E36" s="29"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="74"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25">
         <v>3</v>
       </c>
-      <c r="B37" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>238</v>
-      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="28"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="29">
-        <v>3703</v>
-      </c>
-      <c r="F37" s="18">
-        <v>40</v>
-      </c>
+      <c r="E37" s="29"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="74"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
         <v>4</v>
       </c>
-      <c r="B38" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>230</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="E38" s="29">
-        <v>3652</v>
-      </c>
-      <c r="F38" s="39">
-        <v>20</v>
-      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="39"/>
       <c r="G38" s="74"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
         <v>5</v>
       </c>
-      <c r="B39" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39" s="29">
-        <v>3653</v>
-      </c>
-      <c r="F39" s="29">
-        <v>20</v>
-      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
       <c r="G39" s="74"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
         <v>6</v>
       </c>
-      <c r="B40" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="D40" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="E40" s="29">
-        <v>3654</v>
-      </c>
-      <c r="F40" s="29">
-        <v>20</v>
-      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
         <v>7</v>
       </c>
-      <c r="B41" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E41" s="29">
-        <v>3651</v>
-      </c>
-      <c r="F41" s="29">
-        <v>40</v>
-      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
       <c r="G41" s="74"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
         <v>8</v>
       </c>
-      <c r="B42" s="19">
-        <v>22092026</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>255</v>
-      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="46"/>
-      <c r="E42" s="29">
-        <v>3711</v>
-      </c>
-      <c r="F42" s="29">
-        <v>20</v>
-      </c>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
       <c r="G42" s="74"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BAE2EE8-6EE0-47EF-AACD-9589BF30D51C}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77CA7B6-94B1-453D-9B5F-9472796FA254}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="18" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
     <sheet name="21-09" sheetId="16" r:id="rId16"/>
     <sheet name="22-09" sheetId="17" r:id="rId17"/>
     <sheet name="23-09" sheetId="18" r:id="rId18"/>
+    <sheet name="24-09" sheetId="19" r:id="rId19"/>
+    <sheet name="26-09" sheetId="20" r:id="rId20"/>
+    <sheet name="27-09" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="319">
   <si>
     <t>Date</t>
   </si>
@@ -828,6 +831,192 @@
   </si>
   <si>
     <t>00378-516-31</t>
+  </si>
+  <si>
+    <t>00582-510-31</t>
+  </si>
+  <si>
+    <t>MEDU951011 /6</t>
+  </si>
+  <si>
+    <t>MEDU958286 /2</t>
+  </si>
+  <si>
+    <t>FX46629585</t>
+  </si>
+  <si>
+    <t>FX46635083</t>
+  </si>
+  <si>
+    <t>OOCU976350 /8</t>
+  </si>
+  <si>
+    <t>TCKU704466 /0</t>
+  </si>
+  <si>
+    <t>FSCU805157 /5</t>
+  </si>
+  <si>
+    <t>00053-517-31</t>
+  </si>
+  <si>
+    <t>MSBU796594 /4</t>
+  </si>
+  <si>
+    <t>FJ26597592</t>
+  </si>
+  <si>
+    <t>MSNU921194 /0</t>
+  </si>
+  <si>
+    <t>FJ26597361</t>
+  </si>
+  <si>
+    <t>TIIU443725 /1</t>
+  </si>
+  <si>
+    <t>FJ26597473</t>
+  </si>
+  <si>
+    <t>UETU778883 /2</t>
+  </si>
+  <si>
+    <t>FJ26597436</t>
+  </si>
+  <si>
+    <t>MSDU997113 /6</t>
+  </si>
+  <si>
+    <t>MSMU661001 /2</t>
+  </si>
+  <si>
+    <t>0674611</t>
+  </si>
+  <si>
+    <t>UETU703460 /0</t>
+  </si>
+  <si>
+    <t>0674567</t>
+  </si>
+  <si>
+    <t>MRKU588631 /7</t>
+  </si>
+  <si>
+    <t>UETU682895 /1</t>
+  </si>
+  <si>
+    <t>UETU818706 /0</t>
+  </si>
+  <si>
+    <t>SUDU850406 /0</t>
+  </si>
+  <si>
+    <t>CN6499593</t>
+  </si>
+  <si>
+    <t>CAAU692306 /7</t>
+  </si>
+  <si>
+    <t>CN6229789</t>
+  </si>
+  <si>
+    <t>MRSU415138 /3</t>
+  </si>
+  <si>
+    <t>0167ICS0129</t>
+  </si>
+  <si>
+    <t>0168ICS0007</t>
+  </si>
+  <si>
+    <t>0092ICS0100</t>
+  </si>
+  <si>
+    <t>0092ICS0106</t>
+  </si>
+  <si>
+    <t>0092ICS0025</t>
+  </si>
+  <si>
+    <t>0092ICS0061</t>
+  </si>
+  <si>
+    <t>OOCU568279 /5</t>
+  </si>
+  <si>
+    <t>32460820</t>
+  </si>
+  <si>
+    <t>MSMU923966 /7</t>
+  </si>
+  <si>
+    <t>FX48593058</t>
+  </si>
+  <si>
+    <t>FBLU420928 /6</t>
+  </si>
+  <si>
+    <t>A584769</t>
+  </si>
+  <si>
+    <t>TEXU151862 /6</t>
+  </si>
+  <si>
+    <t>A584615</t>
+  </si>
+  <si>
+    <t>TRIU057483 /0</t>
+  </si>
+  <si>
+    <t>A584616</t>
+  </si>
+  <si>
+    <t>CMAU220385 /0</t>
+  </si>
+  <si>
+    <t>1730449</t>
+  </si>
+  <si>
+    <t>CMAU455459 /8</t>
+  </si>
+  <si>
+    <t>1730443</t>
+  </si>
+  <si>
+    <t>CMAU480173 /8</t>
+  </si>
+  <si>
+    <t>1730445</t>
+  </si>
+  <si>
+    <t>CMAU573921 /4</t>
+  </si>
+  <si>
+    <t>1730441</t>
+  </si>
+  <si>
+    <t>CMAU786292 /7</t>
+  </si>
+  <si>
+    <t>1730447</t>
+  </si>
+  <si>
+    <t>TCNU415361 /5</t>
+  </si>
+  <si>
+    <t>1730400</t>
+  </si>
+  <si>
+    <t>0169ICS0028</t>
+  </si>
+  <si>
+    <t>0167ICS0020</t>
+  </si>
+  <si>
+    <t>0169ICS0018</t>
+  </si>
+  <si>
+    <t>0808ICS0023</t>
   </si>
 </sst>
 </file>
@@ -838,7 +1027,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,6 +1178,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1052,7 +1255,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1225,12 +1428,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1488,6 +1728,106 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1959,8 +2299,8 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1990,7 +2330,117 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="3"/>
-          <a:ext cx="2000250" cy="571497"/>
+          <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFED5443-A9D1-48AE-B070-80A50A658DBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1491BB61-286A-4AF4-A8DA-124EF3AFD0BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="495297"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2046,6 +2496,61 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="485772"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD088C52-137D-409D-B8B6-4B21EF548DA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="514347"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2943,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:D14" si="1">SUM(B8:C8)</f>
+        <f t="shared" ref="D8:D12" si="1">SUM(B8:C8)</f>
         <v>11</v>
       </c>
       <c r="F8" s="3"/>
@@ -2968,214 +3473,223 @@
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B10" s="3">
+        <f>'13-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'13-09'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B11" s="3">
+        <f>'14-09'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <f>'14-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B12" s="3">
+        <f>'15-09'!H1</f>
+        <v>4</v>
+      </c>
+      <c r="C12" s="3">
         <f>'10-09'!H2</f>
         <v>1</v>
       </c>
-      <c r="C10" s="3">
-        <f>'10-09'!H3</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B11" s="3">
-        <f>'10-09'!H3</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="3">
-        <f>'10-09'!H4</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>46278</v>
-      </c>
-      <c r="B12" s="3">
-        <f>'13-09'!H1</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <f>'13-09'!H2</f>
-        <v>2</v>
-      </c>
       <c r="D12" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B13" s="3">
-        <f>'14-09'!H1</f>
-        <v>1</v>
+        <f>'16-09'!H1</f>
+        <v>0</v>
       </c>
       <c r="C13" s="3">
-        <f>'14-09'!H2</f>
-        <v>0</v>
+        <f>'16-09'!H2</f>
+        <v>12</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" ref="D13" si="2">SUM(B13:C13)</f>
+        <v>12</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B14" s="3">
-        <f>'15-09'!H1</f>
-        <v>4</v>
+        <f>'17-09'!H1</f>
+        <v>0</v>
       </c>
       <c r="C14" s="3">
-        <f>'10-09'!H2</f>
-        <v>1</v>
+        <f>'17-09'!H2</f>
+        <v>8</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f t="shared" ref="D14" si="3">SUM(B14:C14)</f>
+        <v>8</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B15" s="3">
-        <f>'16-09'!H1</f>
+        <f>'20-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C15" s="3">
-        <f>'16-09'!H2</f>
-        <v>12</v>
+        <f>'20-09'!H2</f>
+        <v>2</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" ref="D15" si="2">SUM(B15:C15)</f>
-        <v>12</v>
+        <f t="shared" ref="D15" si="4">SUM(B15:C15)</f>
+        <v>2</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B16" s="3">
-        <f>'17-09'!H1</f>
+        <f>'21-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>'17-09'!H2</f>
-        <v>8</v>
+        <f>'21-09'!H2</f>
+        <v>4</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16" si="3">SUM(B16:C16)</f>
-        <v>8</v>
+        <f t="shared" ref="D16" si="5">SUM(B16:C16)</f>
+        <v>4</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="B17" s="3">
-        <f>'20-09'!H1</f>
+        <f>'22-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C17" s="3">
-        <f>'20-09'!H2</f>
-        <v>2</v>
+        <f>'22-09'!H2</f>
+        <v>8</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" ref="D17" si="4">SUM(B17:C17)</f>
-        <v>2</v>
+        <f t="shared" ref="D17" si="6">SUM(B17:C17)</f>
+        <v>8</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B18" s="3">
-        <f>'21-09'!H1</f>
+        <f>'23-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f>'21-09'!H2</f>
-        <v>4</v>
+        <f>'23-09'!H2</f>
+        <v>1</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" ref="D18" si="5">SUM(B18:C18)</f>
-        <v>4</v>
+        <f t="shared" ref="D18" si="7">SUM(B18:C18)</f>
+        <v>1</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B19" s="3">
-        <f>'22-09'!H1</f>
+        <f>'24-09'!J1</f>
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>'22-09'!H2</f>
-        <v>8</v>
+        <f>'24-09'!J2</f>
+        <v>1</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" ref="D19" si="6">SUM(B19:C19)</f>
-        <v>8</v>
+        <f t="shared" ref="D19:D20" si="8">SUM(B19:C19)</f>
+        <v>1</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46288</v>
+        <v>46291</v>
       </c>
       <c r="B20" s="3">
-        <f>'23-09'!H1</f>
+        <f>'26-09'!H1</f>
+        <v>9</v>
+      </c>
+      <c r="C20" s="3">
+        <f>'26-09'!H2</f>
         <v>0</v>
       </c>
-      <c r="C20" s="3">
-        <f>'23-09'!H2</f>
+      <c r="D20" s="4">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" s="88" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B21" s="3">
+        <f>'27-09'!H1</f>
+        <v>11</v>
+      </c>
+      <c r="C21" s="3">
+        <f>'27-09'!H2</f>
         <v>0</v>
       </c>
-      <c r="D20" s="4">
-        <f t="shared" ref="D20" si="7">SUM(B20:C20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>46289</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <f t="shared" ref="D21" si="9">SUM(B21:C21)</f>
+        <v>11</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="88" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -3184,7 +3698,7 @@
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -3196,16 +3710,16 @@
         <v>5</v>
       </c>
       <c r="B24" s="5">
-        <f>SUM(B2:B22)</f>
-        <v>31</v>
+        <f>SUM(B2:B20)</f>
+        <v>39</v>
       </c>
       <c r="C24" s="5">
-        <f>SUM(C2:C22)</f>
-        <v>53</v>
+        <f>SUM(C2:C20)</f>
+        <v>55</v>
       </c>
       <c r="D24" s="5">
-        <f>SUM(D2:D22)</f>
-        <v>84</v>
+        <f>SUM(D2:D20)</f>
+        <v>94</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -8343,7 +8857,7 @@
       </c>
       <c r="H2" s="8">
         <f>COUNTA(C20:C29)-F2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
@@ -8374,7 +8888,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -8542,11 +9056,21 @@
       <c r="A20" s="25">
         <v>1</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="B20" s="19">
+        <v>23092026</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3655</v>
+      </c>
+      <c r="F20" s="18">
+        <v>20</v>
+      </c>
       <c r="N20" s="31"/>
       <c r="O20" s="81"/>
       <c r="P20" s="31"/>
@@ -8741,11 +9265,21 @@
       <c r="A35" s="25">
         <v>1</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="18"/>
+      <c r="B35" s="19">
+        <v>23092026</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="29">
+        <v>3704</v>
+      </c>
+      <c r="F35" s="18">
+        <v>45</v>
+      </c>
       <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8766,7 +9300,6 @@
       <c r="B37" s="19"/>
       <c r="C37" s="28"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="29"/>
       <c r="F37" s="18"/>
       <c r="G37" s="74"/>
     </row>
@@ -8862,6 +9395,651 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F034D3A5-CFFF-48EE-8F0B-F48094E9F832}">
+  <dimension ref="A1:T44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="J1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="H2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8">
+        <f>COUNTA(C20:C29)-H2</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="63"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18"/>
+      <c r="T18"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>23092026</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3704</v>
+      </c>
+      <c r="F20" s="18">
+        <v>45</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20"/>
+      <c r="S20"/>
+      <c r="T20"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="18"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="18"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="18"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="18"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="32"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="32"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="29">
+        <v>3708</v>
+      </c>
+      <c r="F35" s="18">
+        <v>45</v>
+      </c>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C36" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="D36" s="79" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" s="29">
+        <v>3709</v>
+      </c>
+      <c r="F36" s="18">
+        <v>45</v>
+      </c>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C37" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="79" t="s">
+        <v>261</v>
+      </c>
+      <c r="E37" s="78">
+        <v>3710</v>
+      </c>
+      <c r="F37" s="18">
+        <v>45</v>
+      </c>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29">
+        <v>3717</v>
+      </c>
+      <c r="F38" s="39">
+        <v>40</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>263</v>
+      </c>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29">
+        <v>3718</v>
+      </c>
+      <c r="F39" s="29">
+        <v>40</v>
+      </c>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C40" s="79" t="s">
+        <v>264</v>
+      </c>
+      <c r="D40" s="34"/>
+      <c r="E40" s="29">
+        <v>3719</v>
+      </c>
+      <c r="F40" s="29">
+        <v>40</v>
+      </c>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="34">
+        <v>5055347</v>
+      </c>
+      <c r="E41" s="29">
+        <v>3705</v>
+      </c>
+      <c r="F41" s="29">
+        <v>40</v>
+      </c>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>8</v>
+      </c>
+      <c r="B42" s="19">
+        <v>24092026</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" s="29">
+        <v>3720</v>
+      </c>
+      <c r="F42" s="29">
+        <v>40</v>
+      </c>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>9</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>10</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35:F37 F8:F15 F20:F25" xr:uid="{873A6CC2-B0AC-4252-9BA5-5B51ADAB7F71}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F26:F27" xr:uid="{023A5CA8-4A36-4483-9D17-0471F6DF8341}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9476,6 +10654,1417 @@
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3B8252-087A-4065-950E-9C8686BFED82}">
+  <dimension ref="A1:T49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
+        <v>9</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B27:B35,"&lt;&gt;",C27:C35,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C27:C35)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E27:E35,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D8" s="91" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="91" t="s">
+        <v>267</v>
+      </c>
+      <c r="F8" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="90"/>
+      <c r="C9" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D9" s="93" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="92" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D10" s="92" t="s">
+        <v>270</v>
+      </c>
+      <c r="E10" s="92" t="s">
+        <v>271</v>
+      </c>
+      <c r="F10" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="90"/>
+      <c r="C11" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D11" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="92" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D12" s="92" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" s="95" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="92" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="94"/>
+      <c r="C13" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D13" s="92" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" s="95" t="s">
+        <v>276</v>
+      </c>
+      <c r="F13" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="94"/>
+      <c r="C14" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D14" s="92" t="s">
+        <v>277</v>
+      </c>
+      <c r="E14" s="95" t="s">
+        <v>278</v>
+      </c>
+      <c r="F14" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="107" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="96" t="s">
+        <v>279</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>9</v>
+      </c>
+      <c r="B16" s="107"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="96" t="s">
+        <v>280</v>
+      </c>
+      <c r="E16" s="103"/>
+      <c r="F16" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="107"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="96" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="104"/>
+      <c r="F17" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>11</v>
+      </c>
+      <c r="B18" s="97" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D18" s="92" t="s">
+        <v>282</v>
+      </c>
+      <c r="E18" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="F18" s="92" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>12</v>
+      </c>
+      <c r="B19" s="97" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="19">
+        <v>26092026</v>
+      </c>
+      <c r="D19" s="92" t="s">
+        <v>284</v>
+      </c>
+      <c r="E19" s="92" t="s">
+        <v>285</v>
+      </c>
+      <c r="F19" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>13</v>
+      </c>
+      <c r="B20" s="106" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="62"/>
+      <c r="D20" s="92" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25"/>
+      <c r="T25"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>1</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>3</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="18"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>4</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>5</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="18"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>6</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="25">
+        <v>7</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="32"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
+        <v>8</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="32"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>9</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="25"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="35"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="35"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>1</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>2</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>3</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>4</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>5</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>6</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>7</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="74"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
+        <v>8</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="74"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="25">
+        <v>9</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="74"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="25">
+        <v>10</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="E15:E17"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33:F34" xr:uid="{2FD89AD0-6AA4-4C2B-964B-485092017FF2}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F42 F8:F18 F27:F32" xr:uid="{E5CF159C-BA46-4A60-AFDF-8A14E90B8B39}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349A0A24-340E-4657-BA50-75E4DF83C216}">
+  <dimension ref="A1:T49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
+        <v>11</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B27:B35,"&lt;&gt;",C27:C35,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C27:C35)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E27:E35,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="108">
+        <v>1</v>
+      </c>
+      <c r="B8" s="114" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D8" s="118" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="118" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="108">
+        <v>2</v>
+      </c>
+      <c r="B9" s="116" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D9" s="115" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="115" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="115" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="108">
+        <v>3</v>
+      </c>
+      <c r="B10" s="119" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D10" s="115" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="115" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="108">
+        <v>4</v>
+      </c>
+      <c r="B11" s="120"/>
+      <c r="C11" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D11" s="115" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="115" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="108">
+        <v>5</v>
+      </c>
+      <c r="B12" s="121"/>
+      <c r="C12" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D12" s="115" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="117" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="108">
+        <v>6</v>
+      </c>
+      <c r="B13" s="119" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D13" s="115" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="117" t="s">
+        <v>304</v>
+      </c>
+      <c r="F13" s="115" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="108">
+        <v>7</v>
+      </c>
+      <c r="B14" s="120"/>
+      <c r="C14" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D14" s="115" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="117" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="108">
+        <v>8</v>
+      </c>
+      <c r="B15" s="120"/>
+      <c r="C15" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D15" s="118" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="117" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="108">
+        <v>9</v>
+      </c>
+      <c r="B16" s="120"/>
+      <c r="C16" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D16" s="118" t="s">
+        <v>309</v>
+      </c>
+      <c r="E16" s="117" t="s">
+        <v>310</v>
+      </c>
+      <c r="F16" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="108">
+        <v>10</v>
+      </c>
+      <c r="B17" s="120"/>
+      <c r="C17" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D17" s="118" t="s">
+        <v>311</v>
+      </c>
+      <c r="E17" s="117" t="s">
+        <v>312</v>
+      </c>
+      <c r="F17" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="108">
+        <v>11</v>
+      </c>
+      <c r="B18" s="121"/>
+      <c r="C18" s="109">
+        <v>27092026</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="117" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" s="115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="108">
+        <v>12</v>
+      </c>
+      <c r="B19" s="110"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="108">
+        <v>13</v>
+      </c>
+      <c r="B20" s="110"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="108"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>1</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>3</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="18"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>4</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>5</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="18"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>6</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="25">
+        <v>7</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="32"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
+        <v>8</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="32"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>9</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="25"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="35"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="35"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>1</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>2</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>3</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>4</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>5</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="79"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>6</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>7</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="74"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
+        <v>8</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="74"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="25">
+        <v>9</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="74"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="25">
+        <v>10</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F42 F8:F18 F27:F32" xr:uid="{E61E5A94-8428-4EA6-94CA-49751DEB7CF5}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33:F34" xr:uid="{F94C0A9E-1983-44B3-964E-9A78CC5364A0}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77CA7B6-94B1-453D-9B5F-9472796FA254}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF1C95B-F325-4F74-914B-9649531AEC60}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="18" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -1182,15 +1182,18 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1470,7 +1473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1711,6 +1714,36 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1729,44 +1762,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1778,55 +1780,13 @@
     <xf numFmtId="0" fontId="25" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3354,7 +3314,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="3">
-        <f>'02-09'!H1</f>
+        <f>'02-09'!H2</f>
         <v>2</v>
       </c>
       <c r="D3" s="4">
@@ -3372,12 +3332,12 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <f>'03-09'!J2</f>
-        <v>3</v>
+        <f>'03-09'!H2</f>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -3516,12 +3476,12 @@
         <v>4</v>
       </c>
       <c r="C12" s="3">
-        <f>'10-09'!H2</f>
-        <v>1</v>
+        <f>'15-09'!H2</f>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3"/>
     </row>
@@ -3638,16 +3598,16 @@
         <v>46289</v>
       </c>
       <c r="B19" s="3">
-        <f>'24-09'!J1</f>
+        <f>'24-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>'24-09'!J2</f>
-        <v>1</v>
+        <f>'24-09'!H2</f>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" ref="D19:D20" si="8">SUM(B19:C19)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -3669,7 +3629,7 @@
       </c>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" s="88" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46292</v>
       </c>
@@ -3687,7 +3647,7 @@
       </c>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" s="88" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46293</v>
       </c>
@@ -3715,11 +3675,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C20)</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D20)</f>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3779,16 +3739,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4348,16 +4308,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4893,16 +4853,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5328,7 +5288,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="87" t="s">
+      <c r="G37" s="97" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5349,7 +5309,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="87"/>
+      <c r="G38" s="97"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5368,7 +5328,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="87"/>
+      <c r="G39" s="97"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5387,7 +5347,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="87"/>
+      <c r="G40" s="97"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5408,7 +5368,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="87"/>
+      <c r="G41" s="97"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5427,7 +5387,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="87"/>
+      <c r="G42" s="97"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -5446,7 +5406,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="87"/>
+      <c r="G43" s="97"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -5465,7 +5425,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="87"/>
+      <c r="G44" s="97"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -5484,7 +5444,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="87"/>
+      <c r="G45" s="97"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5503,7 +5463,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="87"/>
+      <c r="G46" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5574,16 +5534,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6091,7 +6051,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="87"/>
+      <c r="G38" s="97"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -6112,7 +6072,7 @@
       <c r="F39" s="18">
         <v>40</v>
       </c>
-      <c r="G39" s="87"/>
+      <c r="G39" s="97"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -6133,7 +6093,7 @@
       <c r="F40" s="66">
         <v>40</v>
       </c>
-      <c r="G40" s="87"/>
+      <c r="G40" s="97"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -6144,7 +6104,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="39"/>
-      <c r="G41" s="87"/>
+      <c r="G41" s="97"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -6155,7 +6115,7 @@
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="87"/>
+      <c r="G42" s="97"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -6166,7 +6126,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="87"/>
+      <c r="G43" s="97"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -6177,7 +6137,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="87"/>
+      <c r="G44" s="97"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -6188,7 +6148,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="87"/>
+      <c r="G45" s="97"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -6199,7 +6159,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="87"/>
+      <c r="G46" s="97"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
@@ -6210,7 +6170,7 @@
       <c r="D47" s="46"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="87"/>
+      <c r="G47" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6281,16 +6241,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6937,16 +6897,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7556,16 +7516,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8155,16 +8115,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8868,16 +8828,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9447,16 +9407,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10092,16 +10052,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10706,16 +10666,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10734,22 +10694,22 @@
       <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="82" t="s">
         <v>15</v>
       </c>
     </row>
@@ -10757,19 +10717,19 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="98" t="s">
         <v>287</v>
       </c>
       <c r="C8" s="19">
         <v>26092026</v>
       </c>
-      <c r="D8" s="91" t="s">
+      <c r="D8" s="83" t="s">
         <v>266</v>
       </c>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="83" t="s">
         <v>267</v>
       </c>
-      <c r="F8" s="92" t="s">
+      <c r="F8" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10777,17 +10737,17 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="90"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="19">
         <v>26092026</v>
       </c>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="85" t="s">
         <v>268</v>
       </c>
-      <c r="E9" s="92" t="s">
+      <c r="E9" s="84" t="s">
         <v>269</v>
       </c>
-      <c r="F9" s="92" t="s">
+      <c r="F9" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10795,17 +10755,17 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="90"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="19">
         <v>26092026</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="84" t="s">
         <v>270</v>
       </c>
-      <c r="E10" s="92" t="s">
+      <c r="E10" s="84" t="s">
         <v>271</v>
       </c>
-      <c r="F10" s="92" t="s">
+      <c r="F10" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10813,17 +10773,17 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="90"/>
+      <c r="B11" s="98"/>
       <c r="C11" s="19">
         <v>26092026</v>
       </c>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="84" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="F11" s="92" t="s">
+      <c r="F11" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10831,19 +10791,19 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="99" t="s">
         <v>288</v>
       </c>
       <c r="C12" s="19">
         <v>26092026</v>
       </c>
-      <c r="D12" s="92" t="s">
+      <c r="D12" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="84" t="s">
         <v>157</v>
       </c>
     </row>
@@ -10851,17 +10811,17 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="94"/>
+      <c r="B13" s="99"/>
       <c r="C13" s="19">
         <v>26092026</v>
       </c>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="84" t="s">
         <v>275</v>
       </c>
-      <c r="E13" s="95" t="s">
+      <c r="E13" s="86" t="s">
         <v>276</v>
       </c>
-      <c r="F13" s="92" t="s">
+      <c r="F13" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10869,17 +10829,17 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="19">
         <v>26092026</v>
       </c>
-      <c r="D14" s="92" t="s">
+      <c r="D14" s="84" t="s">
         <v>277</v>
       </c>
-      <c r="E14" s="95" t="s">
+      <c r="E14" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10887,17 +10847,17 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="100" t="s">
         <v>289</v>
       </c>
       <c r="C15" s="19"/>
-      <c r="D15" s="96" t="s">
+      <c r="D15" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10905,13 +10865,13 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="107"/>
+      <c r="B16" s="100"/>
       <c r="C16" s="19"/>
-      <c r="D16" s="96" t="s">
+      <c r="D16" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="103"/>
-      <c r="F16" s="92" t="s">
+      <c r="E16" s="102"/>
+      <c r="F16" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10919,13 +10879,13 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="107"/>
+      <c r="B17" s="100"/>
       <c r="C17" s="19"/>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="E17" s="104"/>
-      <c r="F17" s="92" t="s">
+      <c r="E17" s="103"/>
+      <c r="F17" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10933,19 +10893,19 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="88" t="s">
         <v>290</v>
       </c>
       <c r="C18" s="19">
         <v>26092026</v>
       </c>
-      <c r="D18" s="92" t="s">
+      <c r="D18" s="84" t="s">
         <v>282</v>
       </c>
-      <c r="E18" s="95" t="s">
+      <c r="E18" s="86" t="s">
         <v>283</v>
       </c>
-      <c r="F18" s="92" t="s">
+      <c r="F18" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10953,19 +10913,19 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="88" t="s">
         <v>291</v>
       </c>
       <c r="C19" s="19">
         <v>26092026</v>
       </c>
-      <c r="D19" s="92" t="s">
+      <c r="D19" s="84" t="s">
         <v>284</v>
       </c>
-      <c r="E19" s="92" t="s">
+      <c r="E19" s="84" t="s">
         <v>285</v>
       </c>
-      <c r="F19" s="92" t="s">
+      <c r="F19" s="84" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="7"/>
@@ -10974,17 +10934,17 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="106" t="s">
+      <c r="B20" s="91" t="s">
         <v>292</v>
       </c>
       <c r="C20" s="62"/>
-      <c r="D20" s="92" t="s">
+      <c r="D20" s="84" t="s">
         <v>286</v>
       </c>
-      <c r="E20" s="105" t="s">
+      <c r="E20" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="92" t="s">
+      <c r="F20" s="84" t="s">
         <v>16</v>
       </c>
       <c r="G20" s="7"/>
@@ -10993,27 +10953,27 @@
       <c r="A21" s="17"/>
       <c r="B21" s="61"/>
       <c r="C21" s="62"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="98"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="98"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -11417,16 +11377,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11445,278 +11405,278 @@
       <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="C7" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="82" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="108">
+      <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="109">
+      <c r="C8" s="19">
         <v>27092026</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="E8" s="118" t="s">
+      <c r="E8" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="F8" s="115" t="s">
+      <c r="F8" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="108">
+      <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="70" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="109">
+      <c r="C9" s="19">
         <v>27092026</v>
       </c>
-      <c r="D9" s="115" t="s">
+      <c r="D9" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="E9" s="115" t="s">
+      <c r="E9" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="F9" s="115" t="s">
+      <c r="F9" s="18" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="108">
+      <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="104" t="s">
         <v>317</v>
       </c>
-      <c r="C10" s="109">
+      <c r="C10" s="19">
         <v>27092026</v>
       </c>
-      <c r="D10" s="115" t="s">
+      <c r="D10" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="F10" s="115" t="s">
+      <c r="F10" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="108">
+      <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="120"/>
-      <c r="C11" s="109">
+      <c r="B11" s="105"/>
+      <c r="C11" s="19">
         <v>27092026</v>
       </c>
-      <c r="D11" s="115" t="s">
+      <c r="D11" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="F11" s="115" t="s">
+      <c r="F11" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="108">
+      <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="121"/>
-      <c r="C12" s="109">
+      <c r="B12" s="106"/>
+      <c r="C12" s="19">
         <v>27092026</v>
       </c>
-      <c r="D12" s="115" t="s">
+      <c r="D12" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="E12" s="117" t="s">
+      <c r="E12" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="F12" s="115" t="s">
+      <c r="F12" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="108">
+      <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="119" t="s">
+      <c r="B13" s="104" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="109">
+      <c r="C13" s="19">
         <v>27092026</v>
       </c>
-      <c r="D13" s="115" t="s">
+      <c r="D13" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="E13" s="117" t="s">
+      <c r="E13" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="F13" s="115" t="s">
+      <c r="F13" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="108">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="120"/>
-      <c r="C14" s="109">
+      <c r="B14" s="105"/>
+      <c r="C14" s="19">
         <v>27092026</v>
       </c>
-      <c r="D14" s="115" t="s">
+      <c r="D14" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="E14" s="117" t="s">
+      <c r="E14" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="F14" s="115" t="s">
+      <c r="F14" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="108">
+      <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="120"/>
-      <c r="C15" s="109">
+      <c r="B15" s="105"/>
+      <c r="C15" s="19">
         <v>27092026</v>
       </c>
-      <c r="D15" s="118" t="s">
+      <c r="D15" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="F15" s="115" t="s">
+      <c r="F15" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="108">
+      <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="109">
+      <c r="B16" s="105"/>
+      <c r="C16" s="19">
         <v>27092026</v>
       </c>
-      <c r="D16" s="118" t="s">
+      <c r="D16" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="E16" s="117" t="s">
+      <c r="E16" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="F16" s="115" t="s">
+      <c r="F16" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="108">
+      <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="120"/>
-      <c r="C17" s="109">
+      <c r="B17" s="105"/>
+      <c r="C17" s="19">
         <v>27092026</v>
       </c>
-      <c r="D17" s="118" t="s">
+      <c r="D17" s="24" t="s">
         <v>311</v>
       </c>
-      <c r="E17" s="117" t="s">
+      <c r="E17" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="F17" s="115" t="s">
+      <c r="F17" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="108">
+      <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="121"/>
-      <c r="C18" s="109">
+      <c r="B18" s="106"/>
+      <c r="C18" s="19">
         <v>27092026</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="E18" s="117" t="s">
+      <c r="E18" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="F18" s="115" t="s">
+      <c r="F18" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="108">
+      <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="110"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="111"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="108">
+      <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="110"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="111"/>
-      <c r="F20" s="111"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="108"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="98"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="100"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="98"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -11737,8 +11697,8 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
       <c r="R25" s="31"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
+      <c r="S25"/>
+      <c r="T25"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
@@ -11780,9 +11740,9 @@
       <c r="O27" s="81"/>
       <c r="P27" s="31"/>
       <c r="Q27" s="31"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="88"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
@@ -11898,7 +11858,7 @@
       <c r="A36" s="35"/>
       <c r="B36" s="36"/>
       <c r="C36" s="37"/>
-      <c r="D36" s="88"/>
+      <c r="D36"/>
       <c r="E36" s="38"/>
       <c r="F36" s="35"/>
     </row>
@@ -12117,16 +12077,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12680,16 +12640,16 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -13233,16 +13193,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -13753,16 +13713,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14338,16 +14298,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14851,16 +14811,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15052,7 +15012,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="93" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -15071,7 +15031,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="84"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -15088,7 +15048,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="84"/>
+      <c r="B17" s="94"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -15105,7 +15065,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="84"/>
+      <c r="B18" s="94"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -15122,7 +15082,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="84"/>
+      <c r="B19" s="94"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -15141,7 +15101,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="85"/>
+      <c r="B20" s="95"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -15502,16 +15462,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15579,7 +15539,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="96" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -15600,7 +15560,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="86"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -15619,7 +15579,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="96" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -15642,7 +15602,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="86"/>
+      <c r="B12" s="96"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -15663,7 +15623,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="96"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -15684,7 +15644,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="96"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF1C95B-F325-4F74-914B-9649531AEC60}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05366FF4-16A8-4D50-8ACD-AAD31A608D4E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
@@ -34,6 +34,7 @@
     <sheet name="24-09" sheetId="19" r:id="rId19"/>
     <sheet name="26-09" sheetId="20" r:id="rId20"/>
     <sheet name="27-09" sheetId="21" r:id="rId21"/>
+    <sheet name="28-09" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="328">
   <si>
     <t>Date</t>
   </si>
@@ -1017,6 +1018,33 @@
   </si>
   <si>
     <t>0808ICS0023</t>
+  </si>
+  <si>
+    <t>500089-513-31</t>
+  </si>
+  <si>
+    <t>500096-511-31</t>
+  </si>
+  <si>
+    <t>HASU492916 /6</t>
+  </si>
+  <si>
+    <t>HASU5156746 /8</t>
+  </si>
+  <si>
+    <t>MRSU698006 /4</t>
+  </si>
+  <si>
+    <t>HJCU111021 /6</t>
+  </si>
+  <si>
+    <t>YMLU822002 /6</t>
+  </si>
+  <si>
+    <t>GTSU885207 /7</t>
+  </si>
+  <si>
+    <t>GLDU072442 /9</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1788,6 +1816,9 @@
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2511,6 +2542,61 @@
         <a:xfrm>
           <a:off x="0" y="3"/>
           <a:ext cx="2000250" cy="514347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BAEBE4B-7C1B-4551-9191-60A8FA12A7A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="533397"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3639,11 +3725,11 @@
       </c>
       <c r="C21" s="3">
         <f>'27-09'!H2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" ref="D21" si="9">SUM(B21:C21)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3"/>
     </row>
@@ -3651,9 +3737,18 @@
       <c r="A22" s="2">
         <v>46293</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
+      <c r="B22" s="3">
+        <f>'28-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="3">
+        <f>'28-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="4">
+        <f t="shared" ref="D22" si="10">SUM(B22:C22)</f>
+        <v>0</v>
+      </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3670,12 +3765,12 @@
         <v>5</v>
       </c>
       <c r="B24" s="5">
-        <f>SUM(B2:B20)</f>
-        <v>39</v>
+        <f>SUM(B2:B23)</f>
+        <v>50</v>
       </c>
       <c r="C24" s="5">
-        <f>SUM(C2:C20)</f>
-        <v>50</v>
+        <f>SUM(C2:C23)</f>
+        <v>52</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D20)</f>
@@ -6734,7 +6829,7 @@
         <v>61</v>
       </c>
       <c r="E38" s="29">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="F38" s="66">
         <v>40</v>
@@ -11330,6 +11425,749 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349A0A24-340E-4657-BA50-75E4DF83C216}">
+  <dimension ref="A1:T47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
+        <v>11</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B27:B33,"&lt;&gt;",C27:C33,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C27:C33)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E27:E33,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="104" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="105"/>
+      <c r="C11" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="106"/>
+      <c r="C12" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="104" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="105"/>
+      <c r="C14" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="105"/>
+      <c r="C15" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>9</v>
+      </c>
+      <c r="B16" s="105"/>
+      <c r="C16" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>10</v>
+      </c>
+      <c r="B17" s="105"/>
+      <c r="C17" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>11</v>
+      </c>
+      <c r="B18" s="106"/>
+      <c r="C18" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>12</v>
+      </c>
+      <c r="B19" s="88"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>13</v>
+      </c>
+      <c r="B20" s="88"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25"/>
+      <c r="T25"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>1</v>
+      </c>
+      <c r="B27" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="29">
+        <v>3560</v>
+      </c>
+      <c r="F27" s="66">
+        <v>20</v>
+      </c>
+      <c r="N27" s="31"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27"/>
+      <c r="S27"/>
+      <c r="T27"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E28" s="29">
+        <v>3557</v>
+      </c>
+      <c r="F28" s="66">
+        <v>40</v>
+      </c>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>3</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="18"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>4</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="18"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25">
+        <v>5</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="18"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="25">
+        <v>6</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="18"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="25">
+        <v>7</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="32"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
+      <c r="D34"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>1</v>
+      </c>
+      <c r="B38" s="19">
+        <v>27092026</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="29">
+        <v>3720</v>
+      </c>
+      <c r="E38" s="80">
+        <v>3712</v>
+      </c>
+      <c r="F38" s="29">
+        <v>40</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="D39" s="79">
+        <v>3707</v>
+      </c>
+      <c r="E39" s="29">
+        <v>3715</v>
+      </c>
+      <c r="F39" s="18"/>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="D40" s="79">
+        <v>3706</v>
+      </c>
+      <c r="E40" s="78">
+        <v>3713</v>
+      </c>
+      <c r="F40" s="18"/>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>4</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29">
+        <v>3716</v>
+      </c>
+      <c r="F41" s="39"/>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>5</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="79" t="s">
+        <v>324</v>
+      </c>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29">
+        <v>3662</v>
+      </c>
+      <c r="F42" s="29"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>6</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="79" t="s">
+        <v>325</v>
+      </c>
+      <c r="D43" s="34"/>
+      <c r="E43" s="29">
+        <v>3663</v>
+      </c>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="25">
+        <v>7</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="D44" s="34"/>
+      <c r="E44" s="29">
+        <v>3661</v>
+      </c>
+      <c r="F44" s="29"/>
+      <c r="G44" s="74"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25">
+        <v>8</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D45" s="34"/>
+      <c r="E45" s="29">
+        <v>3664</v>
+      </c>
+      <c r="F45" s="29"/>
+      <c r="G45" s="74"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="25">
+        <v>9</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="74"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="25">
+        <v>10</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F40 F8:F18 F27:F32" xr:uid="{E61E5A94-8428-4EA6-94CA-49751DEB7CF5}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33" xr:uid="{F94C0A9E-1983-44B3-964E-9A78CC5364A0}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCD3411-B5DA-41FF-9644-27C4C45BB121}">
   <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11349,7 +12187,7 @@
       <c r="A1" s="6"/>
       <c r="H1" s="8">
         <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>6</v>
@@ -11428,207 +12266,111 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="70" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>70</v>
-      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="104" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B10" s="107"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="105"/>
-      <c r="C11" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B11" s="107"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="106"/>
-      <c r="C12" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B12" s="107"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="104" t="s">
-        <v>318</v>
-      </c>
-      <c r="C13" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>17</v>
-      </c>
+      <c r="B13" s="107"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B14" s="107"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B15" s="107"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B16" s="107"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B17" s="107"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="19">
-        <v>27092026</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="B18" s="107"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
@@ -11733,9 +12475,9 @@
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="34"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="66"/>
       <c r="N27" s="31"/>
       <c r="O27" s="81"/>
       <c r="P27" s="31"/>
@@ -11750,9 +12492,9 @@
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="29"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="66"/>
       <c r="I28" s="31"/>
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
@@ -11903,10 +12645,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="29"/>
       <c r="G40" s="74"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11914,7 +12656,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="79"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="79"/>
       <c r="E41" s="29"/>
       <c r="F41" s="18"/>
@@ -11925,7 +12667,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="19"/>
-      <c r="C42" s="79"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="79"/>
       <c r="E42" s="78"/>
       <c r="F42" s="18"/>
@@ -11936,7 +12678,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="19"/>
-      <c r="C43" s="79"/>
+      <c r="C43" s="34"/>
       <c r="D43" s="29"/>
       <c r="E43" s="29"/>
       <c r="F43" s="39"/>
@@ -12009,18 +12751,16 @@
       <c r="G49" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B13:B18"/>
+  <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F42 F8:F18 F27:F32" xr:uid="{E61E5A94-8428-4EA6-94CA-49751DEB7CF5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33:F34" xr:uid="{9DD49125-3201-47B9-8F25-DA191F9048EE}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F42 F8:F18 F27:F32" xr:uid="{8238D721-B59B-4555-B936-A88079A56BE6}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33:F34" xr:uid="{F94C0A9E-1983-44B3-964E-9A78CC5364A0}">
-      <formula1>"20,40,45,50"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05366FF4-16A8-4D50-8ACD-AAD31A608D4E}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F984E3-C9F6-4CA4-8FBC-28818639AF77}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="334">
   <si>
     <t>Date</t>
   </si>
@@ -1045,6 +1045,24 @@
   </si>
   <si>
     <t>GLDU072442 /9</t>
+  </si>
+  <si>
+    <t>FFAU501814 /0</t>
+  </si>
+  <si>
+    <t>CAAU640372 /2</t>
+  </si>
+  <si>
+    <t>MSKU148879 /1</t>
+  </si>
+  <si>
+    <t>ML-CN6337956</t>
+  </si>
+  <si>
+    <t>MSKU100022 /7</t>
+  </si>
+  <si>
+    <t>ML-CN6309165</t>
   </si>
 </sst>
 </file>
@@ -1772,6 +1790,9 @@
     <xf numFmtId="14" fontId="26" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1816,9 +1837,6 @@
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3347,7 +3365,7 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -3414,16 +3432,16 @@
         <v>46268</v>
       </c>
       <c r="B4" s="3">
-        <f>'03-09'!J1</f>
+        <f>'03-09'!H1</f>
         <v>2</v>
       </c>
       <c r="C4" s="3">
         <f>'03-09'!H2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -3689,11 +3707,11 @@
       </c>
       <c r="C19" s="3">
         <f>'24-09'!H2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" ref="D19:D20" si="8">SUM(B19:C19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -3770,11 +3788,11 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D20)</f>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -3782,6 +3800,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3834,16 +3853,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4403,16 +4422,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4948,16 +4967,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5383,7 +5402,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="97" t="s">
+      <c r="G37" s="98" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5404,7 +5423,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="97"/>
+      <c r="G38" s="98"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5423,7 +5442,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="97"/>
+      <c r="G39" s="98"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5442,7 +5461,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="97"/>
+      <c r="G40" s="98"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5463,7 +5482,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="97"/>
+      <c r="G41" s="98"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5482,7 +5501,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="97"/>
+      <c r="G42" s="98"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -5501,7 +5520,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="97"/>
+      <c r="G43" s="98"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -5520,7 +5539,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="97"/>
+      <c r="G44" s="98"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -5539,7 +5558,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="97"/>
+      <c r="G45" s="98"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5558,7 +5577,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="97"/>
+      <c r="G46" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5629,16 +5648,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6146,7 +6165,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="97"/>
+      <c r="G38" s="98"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -6167,7 +6186,7 @@
       <c r="F39" s="18">
         <v>40</v>
       </c>
-      <c r="G39" s="97"/>
+      <c r="G39" s="98"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -6188,7 +6207,7 @@
       <c r="F40" s="66">
         <v>40</v>
       </c>
-      <c r="G40" s="97"/>
+      <c r="G40" s="98"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -6199,7 +6218,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="39"/>
-      <c r="G41" s="97"/>
+      <c r="G41" s="98"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -6210,7 +6229,7 @@
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="97"/>
+      <c r="G42" s="98"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -6221,7 +6240,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="97"/>
+      <c r="G43" s="98"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -6232,7 +6251,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="97"/>
+      <c r="G44" s="98"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -6243,7 +6262,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="97"/>
+      <c r="G45" s="98"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -6254,7 +6273,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="97"/>
+      <c r="G46" s="98"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
@@ -6265,7 +6284,7 @@
       <c r="D47" s="46"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="97"/>
+      <c r="G47" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6336,16 +6355,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6992,16 +7011,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7611,16 +7630,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8210,16 +8229,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8923,16 +8942,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9470,53 +9489,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
+      <c r="H1" s="8">
         <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="H2" s="8">
+      <c r="F2" s="8">
         <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
         <v>0</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>1</v>
+      </c>
       <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C20:C29)-H2</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="J2" s="10">
         <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -9525,11 +9544,11 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
         <v>10</v>
       </c>
@@ -9549,7 +9568,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -9559,7 +9578,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -9569,7 +9588,7 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -9579,7 +9598,7 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -9589,7 +9608,7 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -9599,7 +9618,7 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -9609,7 +9628,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -9619,7 +9638,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
@@ -9629,7 +9648,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="20"/>
       <c r="C16" s="7"/>
@@ -10147,16 +10166,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10761,16 +10780,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10812,7 +10831,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="99" t="s">
         <v>287</v>
       </c>
       <c r="C8" s="19">
@@ -10832,7 +10851,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="98"/>
+      <c r="B9" s="99"/>
       <c r="C9" s="19">
         <v>26092026</v>
       </c>
@@ -10850,7 +10869,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="98"/>
+      <c r="B10" s="99"/>
       <c r="C10" s="19">
         <v>26092026</v>
       </c>
@@ -10868,7 +10887,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="98"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="19">
         <v>26092026</v>
       </c>
@@ -10886,7 +10905,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="99" t="s">
+      <c r="B12" s="100" t="s">
         <v>288</v>
       </c>
       <c r="C12" s="19">
@@ -10906,7 +10925,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="99"/>
+      <c r="B13" s="100"/>
       <c r="C13" s="19">
         <v>26092026</v>
       </c>
@@ -10924,7 +10943,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="99"/>
+      <c r="B14" s="100"/>
       <c r="C14" s="19">
         <v>26092026</v>
       </c>
@@ -10942,14 +10961,14 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="101" t="s">
         <v>289</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="102" t="s">
         <v>77</v>
       </c>
       <c r="F15" s="84" t="s">
@@ -10960,12 +10979,12 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="100"/>
+      <c r="B16" s="101"/>
       <c r="C16" s="19"/>
       <c r="D16" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="102"/>
+      <c r="E16" s="103"/>
       <c r="F16" s="84" t="s">
         <v>16</v>
       </c>
@@ -10974,12 +10993,12 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="100"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="19"/>
       <c r="D17" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="E17" s="103"/>
+      <c r="E17" s="104"/>
       <c r="F17" s="84" t="s">
         <v>16</v>
       </c>
@@ -11472,16 +11491,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11563,7 +11582,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="105" t="s">
         <v>317</v>
       </c>
       <c r="C10" s="19">
@@ -11583,7 +11602,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="105"/>
+      <c r="B11" s="106"/>
       <c r="C11" s="19">
         <v>27092026</v>
       </c>
@@ -11601,7 +11620,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="106"/>
+      <c r="B12" s="107"/>
       <c r="C12" s="19">
         <v>27092026</v>
       </c>
@@ -11619,7 +11638,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="104" t="s">
+      <c r="B13" s="105" t="s">
         <v>318</v>
       </c>
       <c r="C13" s="19">
@@ -11639,7 +11658,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="105"/>
+      <c r="B14" s="106"/>
       <c r="C14" s="19">
         <v>27092026</v>
       </c>
@@ -11657,7 +11676,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="105"/>
+      <c r="B15" s="106"/>
       <c r="C15" s="19">
         <v>27092026</v>
       </c>
@@ -11675,7 +11694,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="105"/>
+      <c r="B16" s="106"/>
       <c r="C16" s="19">
         <v>27092026</v>
       </c>
@@ -11693,7 +11712,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="105"/>
+      <c r="B17" s="106"/>
       <c r="C17" s="19">
         <v>27092026</v>
       </c>
@@ -11711,7 +11730,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="106"/>
+      <c r="B18" s="107"/>
       <c r="C18" s="19">
         <v>27092026</v>
       </c>
@@ -12215,16 +12234,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12286,7 +12305,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="107"/>
+      <c r="B10" s="92"/>
       <c r="C10" s="19"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
@@ -12296,7 +12315,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="107"/>
+      <c r="B11" s="92"/>
       <c r="C11" s="19"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
@@ -12306,7 +12325,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="107"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="19"/>
       <c r="D12" s="18"/>
       <c r="E12" s="23"/>
@@ -12316,7 +12335,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="107"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="19"/>
       <c r="D13" s="18"/>
       <c r="E13" s="23"/>
@@ -12326,7 +12345,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="107"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="19"/>
       <c r="D14" s="18"/>
       <c r="E14" s="23"/>
@@ -12336,7 +12355,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="107"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="19"/>
       <c r="D15" s="24"/>
       <c r="E15" s="23"/>
@@ -12346,7 +12365,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="107"/>
+      <c r="B16" s="92"/>
       <c r="C16" s="19"/>
       <c r="D16" s="24"/>
       <c r="E16" s="23"/>
@@ -12356,7 +12375,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="107"/>
+      <c r="B17" s="92"/>
       <c r="C17" s="19"/>
       <c r="D17" s="24"/>
       <c r="E17" s="23"/>
@@ -12366,7 +12385,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="107"/>
+      <c r="B18" s="92"/>
       <c r="C18" s="19"/>
       <c r="D18" s="18"/>
       <c r="E18" s="23"/>
@@ -12645,9 +12664,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="34"/>
+      <c r="C40" s="34" t="s">
+        <v>328</v>
+      </c>
       <c r="D40" s="29"/>
-      <c r="E40" s="80"/>
+      <c r="E40" s="80">
+        <v>3669</v>
+      </c>
       <c r="F40" s="29"/>
       <c r="G40" s="74"/>
     </row>
@@ -12656,9 +12679,13 @@
         <v>2</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="29"/>
+      <c r="C41" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" s="29">
+        <v>3666</v>
+      </c>
       <c r="F41" s="18"/>
       <c r="G41" s="74"/>
     </row>
@@ -12667,9 +12694,15 @@
         <v>3</v>
       </c>
       <c r="B42" s="19"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="78"/>
+      <c r="C42" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="E42" s="78">
+        <v>3667</v>
+      </c>
       <c r="F42" s="18"/>
       <c r="G42" s="74"/>
     </row>
@@ -12678,9 +12711,15 @@
         <v>4</v>
       </c>
       <c r="B43" s="19"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
+      <c r="C43" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="E43" s="29">
+        <v>3668</v>
+      </c>
       <c r="F43" s="39"/>
       <c r="G43" s="74"/>
     </row>
@@ -12817,16 +12856,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -13348,53 +13387,53 @@
     <col min="12" max="16384" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="J1" s="8">
+      <c r="H1" s="8">
         <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="H2" s="8">
+      <c r="F2" s="8">
         <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
         <v>0</v>
       </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>3</v>
+      </c>
       <c r="I2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTA(C20:C29)-H2</f>
-        <v>3</v>
-      </c>
-      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10">
+      <c r="J2" s="10">
         <f>COUNTIF(E20:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-    </row>
-    <row r="4" spans="1:12" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:12" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="11" t="s">
         <v>9</v>
@@ -13403,11 +13442,11 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="13"/>
     </row>
-    <row r="7" spans="1:12" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>10</v>
       </c>
@@ -13427,7 +13466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>1</v>
       </c>
@@ -13448,7 +13487,7 @@
       </c>
       <c r="G8" s="20"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
@@ -13469,7 +13508,7 @@
       </c>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>3</v>
       </c>
@@ -13480,7 +13519,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>4</v>
       </c>
@@ -13491,7 +13530,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>5</v>
       </c>
@@ -13502,7 +13541,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>6</v>
       </c>
@@ -13513,7 +13552,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>7</v>
       </c>
@@ -13524,7 +13563,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>8</v>
       </c>
@@ -13535,7 +13574,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="20"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="20"/>
       <c r="C16" s="7"/>
@@ -13933,16 +13972,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14453,16 +14492,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15038,16 +15077,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15551,16 +15590,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15752,7 +15791,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="94" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -15771,7 +15810,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="94"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -15788,7 +15827,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="94"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -15805,7 +15844,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="94"/>
+      <c r="B18" s="95"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -15822,7 +15861,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="94"/>
+      <c r="B19" s="95"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -15841,7 +15880,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="95"/>
+      <c r="B20" s="96"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -16202,16 +16241,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -16279,7 +16318,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="97" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -16300,7 +16339,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="96"/>
+      <c r="B10" s="97"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -16319,7 +16358,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="97" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -16342,7 +16381,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="96"/>
+      <c r="B12" s="97"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -16363,7 +16402,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="96"/>
+      <c r="B13" s="97"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -16384,7 +16423,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="96"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F984E3-C9F6-4CA4-8FBC-28818639AF77}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DBB408-AAC6-4887-8BF4-7B345316D410}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="26-09" sheetId="20" r:id="rId20"/>
     <sheet name="27-09" sheetId="21" r:id="rId21"/>
     <sheet name="28-09" sheetId="22" r:id="rId22"/>
+    <sheet name="29-09" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="348">
   <si>
     <t>Date</t>
   </si>
@@ -1063,6 +1064,48 @@
   </si>
   <si>
     <t>ML-CN6309165</t>
+  </si>
+  <si>
+    <t>MSMU933118 /2</t>
+  </si>
+  <si>
+    <t>FJ28349555</t>
+  </si>
+  <si>
+    <t>MSMU932960 /5</t>
+  </si>
+  <si>
+    <t>FJ28511677</t>
+  </si>
+  <si>
+    <t>0170ICS0190</t>
+  </si>
+  <si>
+    <t>0170ICS0215</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>00359-515-31</t>
+  </si>
+  <si>
+    <t>00378-505-31</t>
+  </si>
+  <si>
+    <t>00235-509-31</t>
+  </si>
+  <si>
+    <t>00217-507-31</t>
+  </si>
+  <si>
+    <t>ECMU809447 /2</t>
+  </si>
+  <si>
+    <t>M4936024</t>
+  </si>
+  <si>
+    <t>0036-510-31</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1116,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1240,6 +1283,20 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1519,7 +1576,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1837,6 +1894,25 @@
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2578,13 +2654,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>3</xdr:rowOff>
+      <xdr:rowOff>4</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2613,8 +2689,63 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3"/>
-          <a:ext cx="2000250" cy="533397"/>
+          <a:off x="0" y="4"/>
+          <a:ext cx="2000250" cy="466722"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>4</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51D30CF6-BD7C-4AF8-A8F7-477B5E117F00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4"/>
+          <a:ext cx="2000250" cy="466722"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3757,7 +3888,7 @@
       </c>
       <c r="B22" s="3">
         <f>'28-09'!H1</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3">
         <f>'28-09'!H2</f>
@@ -3765,7 +3896,7 @@
       </c>
       <c r="D22" s="4">
         <f t="shared" ref="D22" si="10">SUM(B22:C22)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="3"/>
     </row>
@@ -3773,9 +3904,18 @@
       <c r="A23" s="2">
         <v>46294</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
+      <c r="B23" s="3">
+        <f>'29-09'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="3">
+        <f>'29-09'!H2</f>
+        <v>6</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" ref="D23" si="11">SUM(B23:C23)</f>
+        <v>6</v>
+      </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
@@ -3784,11 +3924,11 @@
       </c>
       <c r="B24" s="5">
         <f>SUM(B2:B23)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D24" s="5">
         <f>SUM(D2:D20)</f>
@@ -12187,7 +12327,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACCD3411-B5DA-41FF-9644-27C4C45BB121}">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
@@ -12205,8 +12345,8 @@
     <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="H1" s="8">
-        <f>COUNTIF(C8:C20,"&lt;&gt;")</f>
-        <v>0</v>
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>2</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>6</v>
@@ -12215,21 +12355,21 @@
     <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="F2" s="8">
-        <f>COUNTIFS(B27:B35,"&lt;&gt;",C27:C35,"VH")</f>
+        <f>COUNTIFS(B21:B29,"&lt;&gt;",C21:C29,"VH")</f>
         <v>0</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8">
-        <f>COUNTA(C27:C35)-F2</f>
+        <f>COUNTA(C21:C29)-F2</f>
         <v>0</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="10">
-        <f>COUNTIF(E27:E35,"VIDE")</f>
+        <f>COUNTIF(E21:E29,"VIDE")</f>
         <v>0</v>
       </c>
     </row>
@@ -12254,7 +12394,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="12">
-        <v>46292</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -12285,21 +12425,41 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="D8" s="110" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="F8" s="111" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="B9" s="70" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="D9" s="113" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" s="111" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="111" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
@@ -12361,6 +12521,624 @@
       <c r="E15" s="23"/>
       <c r="F15" s="18"/>
     </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19"/>
+      <c r="T19"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>1</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="66"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>2</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="66"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>3</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="18"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="18"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>5</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="18"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>6</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="18"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>7</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="32"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>8</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>9</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="35"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="35"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
+        <v>1</v>
+      </c>
+      <c r="B34" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="80">
+        <v>3669</v>
+      </c>
+      <c r="F34" s="29">
+        <v>40</v>
+      </c>
+      <c r="G34" s="74"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>2</v>
+      </c>
+      <c r="B35" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="D35" s="34"/>
+      <c r="E35" s="29">
+        <v>3666</v>
+      </c>
+      <c r="F35" s="18">
+        <v>40</v>
+      </c>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>3</v>
+      </c>
+      <c r="B36" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="E36" s="78">
+        <v>3667</v>
+      </c>
+      <c r="F36" s="18">
+        <v>40</v>
+      </c>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>4</v>
+      </c>
+      <c r="B37" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37" s="29">
+        <v>3668</v>
+      </c>
+      <c r="F37" s="39">
+        <v>40</v>
+      </c>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>5</v>
+      </c>
+      <c r="B38" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C38" s="79" t="s">
+        <v>324</v>
+      </c>
+      <c r="D38" s="29">
+        <v>3662</v>
+      </c>
+      <c r="E38" s="29">
+        <v>3670</v>
+      </c>
+      <c r="F38" s="29">
+        <v>40</v>
+      </c>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>6</v>
+      </c>
+      <c r="B39" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C39" s="79" t="s">
+        <v>325</v>
+      </c>
+      <c r="D39" s="29">
+        <v>3663</v>
+      </c>
+      <c r="E39" s="29">
+        <v>3714</v>
+      </c>
+      <c r="F39" s="29">
+        <v>40</v>
+      </c>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
+        <v>7</v>
+      </c>
+      <c r="B40" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="D40" s="29">
+        <v>3661</v>
+      </c>
+      <c r="E40" s="29">
+        <v>3612</v>
+      </c>
+      <c r="F40" s="29">
+        <v>40</v>
+      </c>
+      <c r="G40" s="74"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="25">
+        <v>8</v>
+      </c>
+      <c r="B41" s="19">
+        <v>28092026</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D41" s="29">
+        <v>3664</v>
+      </c>
+      <c r="E41" s="29">
+        <v>3665</v>
+      </c>
+      <c r="F41" s="29">
+        <v>40</v>
+      </c>
+      <c r="G41" s="74"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="25">
+        <v>9</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="74"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="25">
+        <v>10</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F16:F17" xr:uid="{9DD49125-3201-47B9-8F25-DA191F9048EE}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F34:F36 F8:F15 F21:F26" xr:uid="{8238D721-B59B-4555-B936-A88079A56BE6}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED86BC7-778F-439F-BDC0-BFA64045A9E5}">
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C16,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B21:B29,"&lt;&gt;",C21:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>6</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E21:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="108"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="111"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="112"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="92"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="92"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="92"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="92"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+    </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>9</v>
@@ -12371,439 +13149,430 @@
       <c r="E16" s="23"/>
       <c r="F16" s="18"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="109"/>
+      <c r="T19" s="109"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
-        <v>11</v>
-      </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="18"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
-        <v>12</v>
-      </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="17">
+      <c r="B20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="11" t="s">
+      <c r="E20" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>1</v>
+      </c>
+      <c r="B21" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="29">
+        <v>3708</v>
+      </c>
+      <c r="F21" s="66">
+        <v>45</v>
+      </c>
+      <c r="N21" s="31"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="109"/>
+      <c r="T21" s="109"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>2</v>
+      </c>
+      <c r="B22" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3654</v>
+      </c>
+      <c r="F22" s="66">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25"/>
-      <c r="T25"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>3</v>
+      </c>
+      <c r="B23" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="D23" s="114" t="s">
+        <v>330</v>
+      </c>
+      <c r="E23" s="78">
+        <v>3667</v>
+      </c>
+      <c r="F23" s="18">
+        <v>40</v>
+      </c>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="E24" s="23">
+        <v>3668</v>
+      </c>
+      <c r="F24" s="18">
+        <v>40</v>
+      </c>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>5</v>
+      </c>
+      <c r="B25" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="23">
+        <v>3665</v>
+      </c>
+      <c r="F25" s="18">
+        <v>40</v>
+      </c>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>6</v>
+      </c>
+      <c r="B26" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="23">
+        <v>3651</v>
+      </c>
+      <c r="F26" s="18">
+        <v>40</v>
+      </c>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>7</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="32"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>8</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="32"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>9</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="35"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="35"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="B33" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="16" t="s">
+      <c r="D33" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="25">
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="25">
         <v>1</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="66"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
-    </row>
-    <row r="28" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+      <c r="B34" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="E34" s="21">
+        <v>3611</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="74"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
         <v>2</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="66"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-    </row>
-    <row r="29" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25">
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="74"/>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
         <v>3</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="18"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-    </row>
-    <row r="30" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25">
+      <c r="B36" s="19"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
         <v>4</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="18"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-    </row>
-    <row r="31" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25">
+      <c r="B37" s="19"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="74"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
         <v>5</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="18"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-    </row>
-    <row r="32" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="25">
+      <c r="B38" s="19"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="74"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
         <v>6</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="18"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25">
+      <c r="B39" s="19"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="74"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="25">
         <v>7</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="32"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
-        <v>8</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="32"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="25">
-        <v>9</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="25"/>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37"/>
-      <c r="D36"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="35"/>
-    </row>
-    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="25">
-        <v>1</v>
-      </c>
       <c r="B40" s="19"/>
-      <c r="C40" s="34" t="s">
-        <v>328</v>
-      </c>
+      <c r="C40" s="34"/>
       <c r="D40" s="29"/>
-      <c r="E40" s="80">
-        <v>3669</v>
-      </c>
+      <c r="E40" s="29"/>
       <c r="F40" s="29"/>
       <c r="G40" s="74"/>
     </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B41" s="19"/>
-      <c r="C41" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="29">
-        <v>3666</v>
-      </c>
-      <c r="F41" s="18"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
       <c r="G41" s="74"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B42" s="19"/>
-      <c r="C42" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="E42" s="78">
-        <v>3667</v>
-      </c>
-      <c r="F42" s="18"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
       <c r="G42" s="74"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B43" s="19"/>
-      <c r="C43" s="34" t="s">
-        <v>332</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="E43" s="29">
-        <v>3668</v>
-      </c>
-      <c r="F43" s="39"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
       <c r="G43" s="74"/>
-    </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="25">
-        <v>5</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="79"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="74"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>6</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="74"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
-        <v>7</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="74"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="25">
-        <v>8</v>
-      </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="74"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="25">
-        <v>9</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="74"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="25">
-        <v>10</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F23 F33:F34" xr:uid="{9DD49125-3201-47B9-8F25-DA191F9048EE}">
-      <formula1>"20,40,45,50"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F42 F8:F18 F27:F32" xr:uid="{8238D721-B59B-4555-B936-A88079A56BE6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F16 F21:F26 F34:F36" xr:uid="{C5FD7997-EAA4-4D3E-8C84-A4A8AD74CB4D}">
       <formula1>"20,40,45,50"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F17" xr:uid="{510B70D1-B670-4BEF-AA01-54BB5A0531CD}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -15714,7 +16483,7 @@
         <v>9092026</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>106</v>
+        <v>340</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>107</v>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="709" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DBB408-AAC6-4887-8BF4-7B345316D410}"/>
+  <xr:revisionPtr revIDLastSave="733" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25D97F7B-4981-4BCF-9EA3-B257F9FE0CAB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
@@ -36,6 +36,7 @@
     <sheet name="27-09" sheetId="21" r:id="rId21"/>
     <sheet name="28-09" sheetId="22" r:id="rId22"/>
     <sheet name="29-09" sheetId="23" r:id="rId23"/>
+    <sheet name="30-09" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="350">
   <si>
     <t>Date</t>
   </si>
@@ -1106,6 +1107,12 @@
   </si>
   <si>
     <t>0036-510-31</t>
+  </si>
+  <si>
+    <t>00547-592-31</t>
+  </si>
+  <si>
+    <t>00224-596-31</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1583,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1850,6 +1857,24 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1894,25 +1919,6 @@
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="29" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2757,6 +2763,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40D1875D-5DA1-4637-84FF-E346F935EB0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3"/>
+          <a:ext cx="2000250" cy="495297"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -3496,7 +3557,7 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
@@ -3535,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f t="shared" ref="D2:D7" si="0">SUM(B2:C2)</f>
+        <f t="shared" ref="D2:D6" si="0">SUM(B2:C2)</f>
         <v>4</v>
       </c>
       <c r="F2" s="3"/>
@@ -3614,307 +3675,307 @@
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B7" s="3">
-        <f>'08-09'!H1</f>
+        <f>'09-09'!H1</f>
+        <v>11</v>
+      </c>
+      <c r="C7" s="3">
+        <f>'09-09'!H2</f>
         <v>0</v>
       </c>
-      <c r="C7" s="3">
-        <f>'08-09'!H2</f>
-        <v>0</v>
-      </c>
       <c r="D7" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="D7:D11" si="1">SUM(B7:C7)</f>
+        <v>11</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B8" s="3">
-        <f>'09-09'!H1</f>
-        <v>11</v>
+        <f>'10-09'!H1</f>
+        <v>7</v>
       </c>
       <c r="C8" s="3">
-        <f>'09-09'!H2</f>
-        <v>0</v>
+        <f>'10-09'!H2</f>
+        <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" ref="D8:D12" si="1">SUM(B8:C8)</f>
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46275</v>
+        <v>46278</v>
       </c>
       <c r="B9" s="3">
-        <f>'10-09'!H1</f>
-        <v>7</v>
+        <f>'13-09'!H1</f>
+        <v>0</v>
       </c>
       <c r="C9" s="3">
-        <f>'10-09'!H2</f>
-        <v>1</v>
+        <f>'13-09'!H2</f>
+        <v>2</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B10" s="3">
-        <f>'13-09'!H1</f>
+        <f>'14-09'!H1</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <f>'14-09'!H2</f>
         <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <f>'13-09'!H2</f>
-        <v>2</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B11" s="3">
-        <f>'14-09'!H1</f>
-        <v>1</v>
+        <f>'15-09'!H1</f>
+        <v>4</v>
       </c>
       <c r="C11" s="3">
-        <f>'14-09'!H2</f>
+        <f>'15-09'!H2</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B12" s="3">
-        <f>'15-09'!H1</f>
-        <v>4</v>
+        <f>'16-09'!H1</f>
+        <v>0</v>
       </c>
       <c r="C12" s="3">
-        <f>'15-09'!H2</f>
-        <v>0</v>
+        <f>'16-09'!H2</f>
+        <v>12</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" ref="D12" si="2">SUM(B12:C12)</f>
+        <v>12</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B13" s="3">
-        <f>'16-09'!H1</f>
+        <f>'17-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <f>'16-09'!H2</f>
-        <v>12</v>
+        <f>'17-09'!H2</f>
+        <v>8</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" ref="D13" si="2">SUM(B13:C13)</f>
-        <v>12</v>
+        <f t="shared" ref="D13" si="3">SUM(B13:C13)</f>
+        <v>8</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="B14" s="3">
-        <f>'17-09'!H1</f>
+        <f>'20-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C14" s="3">
-        <f>'17-09'!H2</f>
-        <v>8</v>
+        <f>'20-09'!H2</f>
+        <v>2</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" ref="D14" si="3">SUM(B14:C14)</f>
-        <v>8</v>
+        <f t="shared" ref="D14" si="4">SUM(B14:C14)</f>
+        <v>2</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B15" s="3">
-        <f>'20-09'!H1</f>
+        <f>'21-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C15" s="3">
-        <f>'20-09'!H2</f>
-        <v>2</v>
+        <f>'21-09'!H2</f>
+        <v>4</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" ref="D15" si="4">SUM(B15:C15)</f>
-        <v>2</v>
+        <f t="shared" ref="D15" si="5">SUM(B15:C15)</f>
+        <v>4</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B16" s="3">
-        <f>'21-09'!H1</f>
+        <f>'22-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>'21-09'!H2</f>
-        <v>4</v>
+        <f>'22-09'!H2</f>
+        <v>8</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" ref="D16" si="5">SUM(B16:C16)</f>
-        <v>4</v>
+        <f t="shared" ref="D16" si="6">SUM(B16:C16)</f>
+        <v>8</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B17" s="3">
-        <f>'22-09'!H1</f>
+        <f>'23-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C17" s="3">
-        <f>'22-09'!H2</f>
-        <v>8</v>
+        <f>'23-09'!H2</f>
+        <v>1</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" ref="D17" si="6">SUM(B17:C17)</f>
-        <v>8</v>
+        <f t="shared" ref="D17" si="7">SUM(B17:C17)</f>
+        <v>1</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B18" s="3">
-        <f>'23-09'!H1</f>
+        <f>'24-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f>'23-09'!H2</f>
+        <f>'24-09'!H2</f>
         <v>1</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" ref="D18" si="7">SUM(B18:C18)</f>
+        <f t="shared" ref="D18:D19" si="8">SUM(B18:C18)</f>
         <v>1</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="B19" s="3">
-        <f>'24-09'!H1</f>
+        <f>'26-09'!H1</f>
+        <v>9</v>
+      </c>
+      <c r="C19" s="3">
+        <f>'26-09'!H2</f>
         <v>0</v>
       </c>
-      <c r="C19" s="3">
-        <f>'24-09'!H2</f>
-        <v>1</v>
-      </c>
       <c r="D19" s="4">
-        <f t="shared" ref="D19:D20" si="8">SUM(B19:C19)</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B20" s="3">
-        <f>'26-09'!H1</f>
-        <v>9</v>
+        <f>'27-09'!H1</f>
+        <v>11</v>
       </c>
       <c r="C20" s="3">
-        <f>'26-09'!H2</f>
-        <v>0</v>
+        <f>'27-09'!H2</f>
+        <v>2</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="8"/>
-        <v>9</v>
+        <f t="shared" ref="D20" si="9">SUM(B20:C20)</f>
+        <v>13</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B21" s="3">
-        <f>'27-09'!H1</f>
-        <v>11</v>
+        <f>'28-09'!H1</f>
+        <v>2</v>
       </c>
       <c r="C21" s="3">
-        <f>'27-09'!H2</f>
+        <f>'28-09'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="4">
+        <f t="shared" ref="D21" si="10">SUM(B21:C21)</f>
         <v>2</v>
-      </c>
-      <c r="D21" s="4">
-        <f t="shared" ref="D21" si="9">SUM(B21:C21)</f>
-        <v>13</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B22" s="3">
-        <f>'28-09'!H1</f>
-        <v>2</v>
+        <f>'29-09'!H1</f>
+        <v>0</v>
       </c>
       <c r="C22" s="3">
-        <f>'28-09'!H2</f>
-        <v>0</v>
+        <f>'29-09'!H2</f>
+        <v>6</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" ref="D22" si="10">SUM(B22:C22)</f>
-        <v>2</v>
+        <f t="shared" ref="D22" si="11">SUM(B22:C22)</f>
+        <v>6</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B23" s="3">
-        <f>'29-09'!H1</f>
+        <f>'30-09'!H1</f>
         <v>0</v>
       </c>
       <c r="C23" s="3">
-        <f>'29-09'!H2</f>
-        <v>6</v>
+        <f>'30-09'!H2</f>
+        <v>2</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D23" si="11">SUM(B23:C23)</f>
-        <v>6</v>
+        <f>SUM(B23:C23)</f>
+        <v>2</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -3928,10 +3989,10 @@
       </c>
       <c r="C24" s="5">
         <f>SUM(C2:C23)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" s="5">
-        <f>SUM(D2:D20)</f>
+        <f>SUM(D2:D19)</f>
         <v>93</v>
       </c>
       <c r="E24" s="5"/>
@@ -3993,16 +4054,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -4562,16 +4623,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5107,16 +5168,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -5542,7 +5603,7 @@
       <c r="F37" s="66">
         <v>20</v>
       </c>
-      <c r="G37" s="98" t="s">
+      <c r="G37" s="104" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5563,7 +5624,7 @@
       <c r="F38" s="66">
         <v>20</v>
       </c>
-      <c r="G38" s="98"/>
+      <c r="G38" s="104"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -5582,7 +5643,7 @@
       <c r="F39" s="66">
         <v>20</v>
       </c>
-      <c r="G39" s="98"/>
+      <c r="G39" s="104"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5601,7 +5662,7 @@
       <c r="F40" s="39">
         <v>20</v>
       </c>
-      <c r="G40" s="98"/>
+      <c r="G40" s="104"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5622,7 +5683,7 @@
       <c r="F41" s="29">
         <v>20</v>
       </c>
-      <c r="G41" s="98"/>
+      <c r="G41" s="104"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5641,7 +5702,7 @@
       <c r="F42" s="29">
         <v>20</v>
       </c>
-      <c r="G42" s="98"/>
+      <c r="G42" s="104"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -5660,7 +5721,7 @@
       <c r="F43" s="29">
         <v>20</v>
       </c>
-      <c r="G43" s="98"/>
+      <c r="G43" s="104"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -5679,7 +5740,7 @@
       <c r="F44" s="29">
         <v>20</v>
       </c>
-      <c r="G44" s="98"/>
+      <c r="G44" s="104"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -5698,7 +5759,7 @@
       <c r="F45" s="29">
         <v>20</v>
       </c>
-      <c r="G45" s="98"/>
+      <c r="G45" s="104"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5717,7 +5778,7 @@
       <c r="F46" s="29">
         <v>20</v>
       </c>
-      <c r="G46" s="98"/>
+      <c r="G46" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5788,16 +5849,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -6305,7 +6366,7 @@
       <c r="F38" s="66">
         <v>40</v>
       </c>
-      <c r="G38" s="98"/>
+      <c r="G38" s="104"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="25">
@@ -6326,7 +6387,7 @@
       <c r="F39" s="18">
         <v>40</v>
       </c>
-      <c r="G39" s="98"/>
+      <c r="G39" s="104"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -6347,7 +6408,7 @@
       <c r="F40" s="66">
         <v>40</v>
       </c>
-      <c r="G40" s="98"/>
+      <c r="G40" s="104"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -6358,7 +6419,7 @@
       <c r="D41" s="46"/>
       <c r="E41" s="29"/>
       <c r="F41" s="39"/>
-      <c r="G41" s="98"/>
+      <c r="G41" s="104"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -6369,7 +6430,7 @@
       <c r="D42" s="29"/>
       <c r="E42" s="29"/>
       <c r="F42" s="29"/>
-      <c r="G42" s="98"/>
+      <c r="G42" s="104"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="25">
@@ -6380,7 +6441,7 @@
       <c r="D43" s="46"/>
       <c r="E43" s="29"/>
       <c r="F43" s="29"/>
-      <c r="G43" s="98"/>
+      <c r="G43" s="104"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
@@ -6391,7 +6452,7 @@
       <c r="D44" s="46"/>
       <c r="E44" s="29"/>
       <c r="F44" s="29"/>
-      <c r="G44" s="98"/>
+      <c r="G44" s="104"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="25">
@@ -6402,7 +6463,7 @@
       <c r="D45" s="46"/>
       <c r="E45" s="29"/>
       <c r="F45" s="29"/>
-      <c r="G45" s="98"/>
+      <c r="G45" s="104"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -6413,7 +6474,7 @@
       <c r="D46" s="46"/>
       <c r="E46" s="29"/>
       <c r="F46" s="29"/>
-      <c r="G46" s="98"/>
+      <c r="G46" s="104"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
@@ -6424,7 +6485,7 @@
       <c r="D47" s="46"/>
       <c r="E47" s="29"/>
       <c r="F47" s="29"/>
-      <c r="G47" s="98"/>
+      <c r="G47" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6495,16 +6556,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7151,16 +7212,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -7770,16 +7831,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -8369,16 +8430,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9082,16 +9143,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -9661,16 +9722,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10306,16 +10367,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10920,16 +10981,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -10971,7 +11032,7 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="105" t="s">
         <v>287</v>
       </c>
       <c r="C8" s="19">
@@ -10991,7 +11052,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="99"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="19">
         <v>26092026</v>
       </c>
@@ -11009,7 +11070,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="99"/>
+      <c r="B10" s="105"/>
       <c r="C10" s="19">
         <v>26092026</v>
       </c>
@@ -11027,7 +11088,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="99"/>
+      <c r="B11" s="105"/>
       <c r="C11" s="19">
         <v>26092026</v>
       </c>
@@ -11045,7 +11106,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="100" t="s">
+      <c r="B12" s="106" t="s">
         <v>288</v>
       </c>
       <c r="C12" s="19">
@@ -11065,7 +11126,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="100"/>
+      <c r="B13" s="106"/>
       <c r="C13" s="19">
         <v>26092026</v>
       </c>
@@ -11083,7 +11144,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="100"/>
+      <c r="B14" s="106"/>
       <c r="C14" s="19">
         <v>26092026</v>
       </c>
@@ -11101,14 +11162,14 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="107" t="s">
         <v>289</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="108" t="s">
         <v>77</v>
       </c>
       <c r="F15" s="84" t="s">
@@ -11119,12 +11180,12 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="101"/>
+      <c r="B16" s="107"/>
       <c r="C16" s="19"/>
       <c r="D16" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="E16" s="103"/>
+      <c r="E16" s="109"/>
       <c r="F16" s="84" t="s">
         <v>16</v>
       </c>
@@ -11133,12 +11194,12 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="101"/>
+      <c r="B17" s="107"/>
       <c r="C17" s="19"/>
       <c r="D17" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="E17" s="104"/>
+      <c r="E17" s="110"/>
       <c r="F17" s="84" t="s">
         <v>16</v>
       </c>
@@ -11631,16 +11692,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -11722,7 +11783,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="111" t="s">
         <v>317</v>
       </c>
       <c r="C10" s="19">
@@ -11742,7 +11803,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="106"/>
+      <c r="B11" s="112"/>
       <c r="C11" s="19">
         <v>27092026</v>
       </c>
@@ -11760,7 +11821,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="107"/>
+      <c r="B12" s="113"/>
       <c r="C12" s="19">
         <v>27092026</v>
       </c>
@@ -11778,7 +11839,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="105" t="s">
+      <c r="B13" s="111" t="s">
         <v>318</v>
       </c>
       <c r="C13" s="19">
@@ -11798,7 +11859,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="106"/>
+      <c r="B14" s="112"/>
       <c r="C14" s="19">
         <v>27092026</v>
       </c>
@@ -11816,7 +11877,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="106"/>
+      <c r="B15" s="112"/>
       <c r="C15" s="19">
         <v>27092026</v>
       </c>
@@ -11834,7 +11895,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="106"/>
+      <c r="B16" s="112"/>
       <c r="C16" s="19">
         <v>27092026</v>
       </c>
@@ -11852,7 +11913,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="106"/>
+      <c r="B17" s="112"/>
       <c r="C17" s="19">
         <v>27092026</v>
       </c>
@@ -11870,7 +11931,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="107"/>
+      <c r="B18" s="113"/>
       <c r="C18" s="19">
         <v>27092026</v>
       </c>
@@ -12374,16 +12435,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -12431,13 +12492,13 @@
       <c r="C8" s="19">
         <v>28092026</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="94" t="s">
         <v>334</v>
       </c>
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="94" t="s">
         <v>335</v>
       </c>
-      <c r="F8" s="111" t="s">
+      <c r="F8" s="95" t="s">
         <v>70</v>
       </c>
     </row>
@@ -12451,13 +12512,13 @@
       <c r="C9" s="19">
         <v>28092026</v>
       </c>
-      <c r="D9" s="113" t="s">
+      <c r="D9" s="97" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="111" t="s">
+      <c r="E9" s="95" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="111" t="s">
+      <c r="F9" s="95" t="s">
         <v>70</v>
       </c>
     </row>
@@ -13012,16 +13073,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -13063,21 +13124,21 @@
       <c r="A8" s="17">
         <v>1</v>
       </c>
-      <c r="B8" s="108"/>
+      <c r="B8" s="93"/>
       <c r="C8" s="19"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="111"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="95"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="112"/>
+      <c r="B9" s="96"/>
       <c r="C9" s="19"/>
-      <c r="D9" s="113"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="111"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
@@ -13176,8 +13237,8 @@
       <c r="P19" s="31"/>
       <c r="Q19" s="31"/>
       <c r="R19" s="31"/>
-      <c r="S19" s="109"/>
-      <c r="T19" s="109"/>
+      <c r="S19"/>
+      <c r="T19"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
@@ -13229,9 +13290,9 @@
       <c r="O21" s="81"/>
       <c r="P21" s="31"/>
       <c r="Q21" s="31"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
+      <c r="R21"/>
+      <c r="S21"/>
+      <c r="T21"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
@@ -13268,7 +13329,7 @@
       <c r="C23" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="D23" s="114" t="s">
+      <c r="D23" s="98" t="s">
         <v>330</v>
       </c>
       <c r="E23" s="78">
@@ -13397,7 +13458,7 @@
       <c r="A30" s="35"/>
       <c r="B30" s="36"/>
       <c r="C30" s="37"/>
-      <c r="D30" s="109"/>
+      <c r="D30"/>
       <c r="E30" s="38"/>
       <c r="F30" s="35"/>
     </row>
@@ -13568,6 +13629,529 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F17" xr:uid="{510B70D1-B670-4BEF-AA01-54BB5A0531CD}">
       <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE8299D-A573-45A4-8EA0-3FF7076E28B8}">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.42578125" style="21"/>
+    <col min="11" max="11" width="14.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="H1" s="8">
+        <f>COUNTIF(C8:C15,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="F2" s="8">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8">
+        <f>COUNTA(C20:C29)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="12">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>1</v>
+      </c>
+      <c r="B8" s="17"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2</v>
+      </c>
+      <c r="B9" s="53"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>4</v>
+      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>6</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>8</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>1</v>
+      </c>
+      <c r="B20" s="19">
+        <v>30092026</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20" s="79" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="29">
+        <v>3709</v>
+      </c>
+      <c r="F20" s="18">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+      <c r="B21" s="19">
+        <v>30092026</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="78">
+        <v>3710</v>
+      </c>
+      <c r="F21" s="18">
+        <v>45</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="25"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25">
+        <v>5</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25">
+        <v>6</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="25"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25">
+        <v>7</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="25"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="25">
+        <v>8</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="25"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>9</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="25"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25">
+        <v>10</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25">
+        <v>11</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="25"/>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="25">
+        <v>1</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="25">
+        <v>2</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="25">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25">
+        <v>4</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="25">
+        <v>5</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40">
+        <v>7</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="25"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F41 F16" xr:uid="{E6BD5D6F-9413-4BD9-A567-BD5097D933EA}">
+      <formula1>"20,40,45,50"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F15 F20:F21" xr:uid="{43477B74-5097-4BDB-8038-F8500D404237}">
+      <formula1>"20,40,45,50"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13625,16 +14209,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14188,16 +14772,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -14741,16 +15325,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15261,16 +15845,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -15846,16 +16430,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -16359,16 +16943,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -16560,7 +17144,7 @@
       <c r="A15" s="17">
         <v>8</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="100" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="64"/>
@@ -16579,7 +17163,7 @@
       <c r="A16" s="17">
         <v>9</v>
       </c>
-      <c r="B16" s="95"/>
+      <c r="B16" s="101"/>
       <c r="C16" s="64"/>
       <c r="D16" s="24" t="s">
         <v>119</v>
@@ -16596,7 +17180,7 @@
       <c r="A17" s="17">
         <v>10</v>
       </c>
-      <c r="B17" s="95"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="64"/>
       <c r="D17" s="18" t="s">
         <v>121</v>
@@ -16613,7 +17197,7 @@
       <c r="A18" s="17">
         <v>11</v>
       </c>
-      <c r="B18" s="95"/>
+      <c r="B18" s="101"/>
       <c r="C18" s="64"/>
       <c r="D18" s="18" t="s">
         <v>123</v>
@@ -16630,7 +17214,7 @@
       <c r="A19" s="17">
         <v>12</v>
       </c>
-      <c r="B19" s="95"/>
+      <c r="B19" s="101"/>
       <c r="C19" s="19">
         <v>9092026</v>
       </c>
@@ -16649,7 +17233,7 @@
       <c r="A20" s="17">
         <v>13</v>
       </c>
-      <c r="B20" s="96"/>
+      <c r="B20" s="102"/>
       <c r="C20" s="19">
         <v>9092026</v>
       </c>
@@ -17010,16 +17594,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -17087,7 +17671,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="103" t="s">
         <v>142</v>
       </c>
       <c r="C9" s="19">
@@ -17108,7 +17692,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="97"/>
+      <c r="B10" s="103"/>
       <c r="C10" s="19">
         <v>10092026</v>
       </c>
@@ -17127,7 +17711,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="103" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="19">
@@ -17150,7 +17734,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="97"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="19">
         <v>10092026</v>
       </c>
@@ -17171,7 +17755,7 @@
       <c r="A13" s="17">
         <v>6</v>
       </c>
-      <c r="B13" s="97"/>
+      <c r="B13" s="103"/>
       <c r="C13" s="19">
         <v>10092026</v>
       </c>
@@ -17192,7 +17776,7 @@
       <c r="A14" s="17">
         <v>7</v>
       </c>
-      <c r="B14" s="97"/>
+      <c r="B14" s="103"/>
       <c r="C14" s="19">
         <v>10092026</v>
       </c>

--- a/Fiche de mouvement _09-2026.xlsx
+++ b/Fiche de mouvement _09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="733" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25D97F7B-4981-4BCF-9EA3-B257F9FE0CAB}"/>
+  <xr:revisionPtr revIDLastSave="741" documentId="8_{110EE0FD-1A37-4947-891C-6105C32C194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{350B9F5D-DBD6-454B-86E5-D0101AE5A2DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
+    <workbookView minimized="1" xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12690" firstSheet="9" activeTab="22" xr2:uid="{403A34A7-5625-45D4-A0A1-FEBBA2615750}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -1295,15 +1295,18 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -13511,11 +13514,11 @@
       <c r="D34" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="29">
         <v>3611</v>
       </c>
-      <c r="F34" s="18" t="s">
-        <v>70</v>
+      <c r="F34" s="18">
+        <v>40</v>
       </c>
       <c r="G34" s="74"/>
     </row>
@@ -13523,11 +13526,21 @@
       <c r="A35" s="25">
         <v>2</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="18"/>
+      <c r="B35" s="19">
+        <v>29092026</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="34">
+        <v>3712</v>
+      </c>
+      <c r="E35" s="29">
+        <v>3613</v>
+      </c>
+      <c r="F35" s="18">
+        <v>45</v>
+      </c>
       <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
